--- a/docs/xlsx/jobs-2026-10-23.xlsx
+++ b/docs/xlsx/jobs-2026-10-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="580">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1729 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>2027 Forestry Summer Internship - Knoxville, TN</t>
+  </si>
+  <si>
+    <t>American Forest Management, Inc.</t>
+  </si>
+  <si>
+    <t>Knoxville, TN</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$16 - $17 per hour</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-forestry-summer-internship---knoxville-tn-knoxville-tennessee/8951563701</t>
+  </si>
+  <si>
+    <t>Advocacy Assistant (Anticoagulant Rodenticides)</t>
+  </si>
+  <si>
+    <t>Birds Connect Seattle</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$25 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-advocacy-assistant-anticoagulant-rodenticides-seattle-washington/3294637981</t>
+  </si>
+  <si>
+    <t>AmeriCorps Crew Leader or Crew Member - Springfield, MO</t>
+  </si>
+  <si>
+    <t>Conservation Corps Minnesota and Iowa</t>
+  </si>
+  <si>
+    <t>Springfield, MO</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$2,400 - $2,500 per month</t>
+  </si>
+  <si>
+    <t>outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-crew-leader-or-crew-member---springfield-mo-springfield-missouri/2774919257</t>
+  </si>
+  <si>
+    <t>AmeriCorps Crew Member</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Conservancy</t>
+  </si>
+  <si>
+    <t>Estes Park, CO</t>
+  </si>
+  <si>
+    <t>$500 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-crew-member-estes-park-colorado/3298769314</t>
+  </si>
+  <si>
+    <t>AmeriCorps Field Specialist - Springfield, MO</t>
+  </si>
+  <si>
+    <t>$2,600 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-americorps-field-specialist---springfield-mo-springfield-missouri/8138573619</t>
+  </si>
+  <si>
+    <t>Assistant Crew Leader</t>
+  </si>
+  <si>
+    <t>Southern Appalachian Wilderness Stewards (SAWS)</t>
+  </si>
+  <si>
+    <t>Roanoke, VA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$23 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-crew-leader-roanoke-virginia/5687362345</t>
+  </si>
+  <si>
+    <t>Assistant Region Manager – State Lands</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$102,888 - $119,976 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-region-manager--state-lands-olympia-washington/2350817221</t>
+  </si>
+  <si>
+    <t>Caretaker</t>
+  </si>
+  <si>
+    <t>Canyonlands Field Institute</t>
+  </si>
+  <si>
+    <t>Moab, UT</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-caretaker-moab-utah/6612331911</t>
+  </si>
+  <si>
+    <t>Chief Advancement Officer</t>
+  </si>
+  <si>
+    <t>Lowcountry Land Trust</t>
+  </si>
+  <si>
+    <t>Charleston, SC</t>
+  </si>
+  <si>
+    <t>$105,000 - $118,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-chief-advancement-officer-charleston-south-carolina/4229472843</t>
+  </si>
+  <si>
+    <t>Conservation Corps - Field Coordinator</t>
+  </si>
+  <si>
+    <t>$1,057.69 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-corps---field-coordinator-estes-park-colorado/5786554690</t>
+  </si>
+  <si>
+    <t>Conservation Research Analyst</t>
+  </si>
+  <si>
+    <t>Teton Raptor Center</t>
+  </si>
+  <si>
+    <t>Jackson, WY</t>
+  </si>
+  <si>
+    <t>Equivalent to GS grade 8</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-research-analyst-jackson-wyoming/6400825489</t>
+  </si>
+  <si>
+    <t>Coqui Response FIeld Crew</t>
+  </si>
+  <si>
+    <t>O'ahu Invasive Species Committee</t>
+  </si>
+  <si>
+    <t>Kailua, HI</t>
+  </si>
+  <si>
+    <t>$24 per hour</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-coqui-response-field-crew-kailua-hawaii/1042475481</t>
+  </si>
+  <si>
+    <t>Data Services Manager</t>
+  </si>
+  <si>
+    <t>Save Mount Diablo - Walnut Creek, CA</t>
+  </si>
+  <si>
+    <t>Walnut Creek, CA</t>
+  </si>
+  <si>
+    <t>$62,000 - $72,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-data-services-manager-walnut-creek-california/9616923600</t>
+  </si>
+  <si>
+    <t>Director of Advancement</t>
+  </si>
+  <si>
+    <t>North County Land Trust</t>
+  </si>
+  <si>
+    <t>Leominster, MA</t>
+  </si>
+  <si>
+    <t>$68,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-advancement-leominster-massachusetts/4617412923</t>
+  </si>
+  <si>
+    <t>Director of Conservation &amp; Storytelling</t>
+  </si>
+  <si>
+    <t>The Great Elephant Migration</t>
+  </si>
+  <si>
+    <t>Remote, Asia</t>
+  </si>
+  <si>
+    <t>$100,000 - $120,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-conservation--storytelling-remote-asia/7217275212</t>
+  </si>
+  <si>
+    <t>District Forester (Burney Forestry District)</t>
+  </si>
+  <si>
+    <t>Sierra Pacific Industries</t>
+  </si>
+  <si>
+    <t>Burney, CA</t>
+  </si>
+  <si>
+    <t>$65,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-forester-burney-forestry-district-burney-california/6120204936</t>
+  </si>
+  <si>
+    <t>Duke Campus Farm Program Manager</t>
+  </si>
+  <si>
+    <t>Duke Campus Farm</t>
+  </si>
+  <si>
+    <t>Durham, NC</t>
+  </si>
+  <si>
+    <t>$65,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-duke-campus-farm-program-manager-durham-north-carolina/7907083426</t>
+  </si>
+  <si>
+    <t>Education Interpreter</t>
+  </si>
+  <si>
+    <t>South Carolina Aquarium</t>
+  </si>
+  <si>
+    <t>$15 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education-interpreter-charleston-south-carolina/9159391455</t>
+  </si>
+  <si>
+    <t>Environmental Scientist (JC-536060)</t>
+  </si>
+  <si>
+    <t>California State Water Resources Control Board</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$4,551 - $9,601 per month</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-scientist-jc-536060-sacramento-california/3121649461</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Bighorn Society</t>
+  </si>
+  <si>
+    <t>Remote, CO</t>
+  </si>
+  <si>
+    <t>$7,500 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-remote-colorado/2168047104</t>
+  </si>
+  <si>
+    <t>Facilities Manager</t>
+  </si>
+  <si>
+    <t>Triangle Land Conservancy</t>
+  </si>
+  <si>
+    <t>$58,000 - $60,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-facilities-manager-durham-north-carolina/8205039428</t>
+  </si>
+  <si>
+    <t>Farm and Climate Manager</t>
+  </si>
+  <si>
+    <t>Center for Land-Based Learning</t>
+  </si>
+  <si>
+    <t>Woodland, CA</t>
+  </si>
+  <si>
+    <t>$72,384 - $89,880 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-farm-and-climate-manager-woodland-california/3717598876</t>
+  </si>
+  <si>
+    <t>Field Crew Member</t>
+  </si>
+  <si>
+    <t>Conservation Corps MN/IA</t>
+  </si>
+  <si>
+    <t>Des Moines, IA</t>
+  </si>
+  <si>
+    <t>$2,400 per month</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-crew-member-des-moines-iowa/8744490664</t>
+  </si>
+  <si>
+    <t>Invasive Plant Management Individual Placements - NPS National Capital Region</t>
+  </si>
+  <si>
+    <t>Appalachian Conservation Corps and the National Park Service</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>$800 per week</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-invasive-plant-management-individual-placements---nps-national-capital-region-washington-dc-dc/4927813399</t>
+  </si>
+  <si>
+    <t>James River Association - Coastal Restoration Engagement and Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>James River Association</t>
+  </si>
+  <si>
+    <t>Williamsburg, VA</t>
+  </si>
+  <si>
+    <t>$50,000 - $60,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-marine-biology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-james-river-association---coastal-restoration-engagement-and-outreach-coordinator-williamsburg-virginia/9492168137</t>
+  </si>
+  <si>
+    <t>Land Programs Manager</t>
+  </si>
+  <si>
+    <t>Scenic Rivers Land Trust</t>
+  </si>
+  <si>
+    <t>Annapolis, MD</t>
+  </si>
+  <si>
+    <t>$60,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land-programs-manager-annapolis-maryland/7045398586</t>
+  </si>
+  <si>
+    <t>Natural Resource Management Technician</t>
+  </si>
+  <si>
+    <t>Virginia Forestry and Wildlife Group</t>
+  </si>
+  <si>
+    <t>Charlottesville, VA</t>
+  </si>
+  <si>
+    <t>$17 - $19 per hour</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resource-management-technician-charlottesville-virginia/5605364873</t>
+  </si>
+  <si>
+    <t>PCSU Forestry Field Crew Leader</t>
+  </si>
+  <si>
+    <t>Hawaii Divison of Forestry and Wildlife- Maui Branch</t>
+  </si>
+  <si>
+    <t>Kahului, HI</t>
+  </si>
+  <si>
+    <t>$4,220 per month</t>
+  </si>
+  <si>
+    <t>forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-pcsu-forestry-field-crew-leader-kahului-hawaii/3347939852</t>
+  </si>
+  <si>
+    <t>Recreation Technician Crew Leader</t>
+  </si>
+  <si>
+    <t>Arizona Conservation Corps</t>
+  </si>
+  <si>
+    <t>Tonto Basin, AZ</t>
+  </si>
+  <si>
+    <t>$900 per week</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-recreation-technician-crew-leader-tonto-basin-arizona/1486729101</t>
+  </si>
+  <si>
+    <t>Senior Manager - Communications &amp; External Affairs</t>
+  </si>
+  <si>
+    <t>Great Lakes Observing System (GLOS)</t>
+  </si>
+  <si>
+    <t>Ann Arbor, MI</t>
+  </si>
+  <si>
+    <t>$98,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-manager---communications--external-affairs-ann-arbor-michigan/8350056337</t>
+  </si>
+  <si>
+    <t>Sonoran Pronghorn Recovery Project Lead</t>
+  </si>
+  <si>
+    <t>Arizona Game and Fish Department</t>
+  </si>
+  <si>
+    <t>Yuma, AZ</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sonoran-pronghorn-recovery-project-lead-yuma-arizona/7584537293</t>
+  </si>
+  <si>
+    <t>Visitor Outreach Technician (NPS, Joshua Tree National Park)</t>
+  </si>
+  <si>
+    <t>Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Twentynine Palms, CA</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-visitor-outreach-technician-nps-joshua-tree-national-park-twentynine-palms-california/8031913490</t>
+  </si>
+  <si>
+    <t>Visitor Services Assistant (NPS, Zion National Park)</t>
+  </si>
+  <si>
+    <t>Springdale, UT</t>
+  </si>
+  <si>
+    <t>$15.50 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-visitor-services-assistant-nps-zion-national-park-springdale-utah/2568532072</t>
+  </si>
+  <si>
+    <t>APOYO ESCOLAR - CENTRO BARRIAL LA LUCILA</t>
+  </si>
+  <si>
+    <t>Centros Barriales - Municipalidad de Vicente López</t>
+  </si>
+  <si>
+    <t>Florida, Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Children Youth, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/99a10b9e83a545f18a202472342374b5-apoyo-escolar-centro-barrial-la-lucila-centros-barriales-municipalidad-de-vicente-lopez-florida</t>
+  </si>
+  <si>
+    <t>Associate Community Organizer</t>
+  </si>
+  <si>
+    <t>Direct Action &amp; Research Training Center</t>
+  </si>
+  <si>
+    <t>Kansas City, Kansas</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7d8ef41d4904a9989b29bc2fab2a6d6-associate-community-organizer-direct-action-research-training-center-kansas-city</t>
+  </si>
+  <si>
+    <t>Bilingual Case Manager</t>
+  </si>
+  <si>
+    <t>LiftUp Communities</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 52000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Financial Literacy Personal Finance, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e7bb25759cb044c4b250d6a14486528d-bilingual-case-manager-liftup-communities-chicago</t>
+  </si>
+  <si>
+    <t>Chapter and Walk Manager - Western Region</t>
+  </si>
+  <si>
+    <t>Cure JM Foundation</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 0.00 - 30000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Children Youth, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/19005619b9a54b9397997408390a6a2c-chapter-and-walk-manager-western-region-cure-jm-foundation-leesburg</t>
+  </si>
+  <si>
+    <t>Chief of Staff to the CEO</t>
+  </si>
+  <si>
+    <t>Partners for Rural Impact</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dab74d3c44014dc0935636fec454c9f9-chief-of-staff-to-the-ceo-partners-for-rural-impact-berea</t>
+  </si>
+  <si>
+    <t>Clinical Director</t>
+  </si>
+  <si>
+    <t>Neotree</t>
+  </si>
+  <si>
+    <t>Remote (GB)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Health Medicine, Reproductive Health Rights, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f642c4c358141609f3a28fb6810c4cf-clinical-director-neotree-london</t>
+  </si>
+  <si>
+    <t>Contracts Manager</t>
+  </si>
+  <si>
+    <t>CAI</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/838f34d33a6c4a58bb6a65a76ae60801-contracts-manager-cai-new-york</t>
+  </si>
+  <si>
+    <t>Deputy Director of Communications</t>
+  </si>
+  <si>
+    <t>Equimundo</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/771ed9dcf099432c99148c57a34111c9-deputy-director-of-communications-equimundo-washington</t>
+  </si>
+  <si>
+    <t>Development &amp; Events Associate</t>
+  </si>
+  <si>
+    <t>Careers In Nonprofits, Inc.</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/454b910acc0d4ca69f5e4faaaacf315b-development-events-associate-careers-in-nonprofits-inc-washington</t>
+  </si>
+  <si>
+    <t>Development Consultant</t>
+  </si>
+  <si>
+    <t>Mengo Hospital Partners</t>
+  </si>
+  <si>
+    <t>Remote (Dallas, Texas)</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c0163dec4d14003936d152fd2def52f-development-consultant-mengo-hospital-partners-dallas</t>
+  </si>
+  <si>
+    <t>Development Coordinator (PT)</t>
+  </si>
+  <si>
+    <t>Seattle Out &amp; Proud</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 33.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Lgbtq, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d80a5764478148b7a5ccc62feaf23352-development-coordinator-pt-seattle-out-proud-seattle</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>1.5°Climate Strategies Group</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1168f66a10d442ebab928036c5adcb7a-development-director-15climate-strategies-group-seattle</t>
+  </si>
+  <si>
+    <t>Development Director/Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>Kehilat Romemu</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5622b7e90ab24c90913a1fb8d7c15551-development-directormajor-gifts-officer-kehilat-romemu-new-york</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>My Voice Music</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ce9d3202b05d4cbca316dd9ae126c8b0-development-manager-my-voice-music-portland</t>
+  </si>
+  <si>
+    <t>Development Operations and Donor Engagement Manager</t>
+  </si>
+  <si>
+    <t>The Opportunity Network</t>
+  </si>
+  <si>
+    <t>USD 70433.00 - 77250.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab1c439e944e40d58b9dc8b7faa8ffbe-development-operations-and-donor-engagement-manager-the-opportunity-network-new-york</t>
+  </si>
+  <si>
+    <t>Development Operations Manager</t>
+  </si>
+  <si>
+    <t>National Park Trust</t>
+  </si>
+  <si>
+    <t>Rockville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f890006010984a07a064dcc272c141cc-development-operations-manager-national-park-trust-rockville</t>
+  </si>
+  <si>
+    <t>Digital Communications Manager</t>
+  </si>
+  <si>
+    <t>United States of Care</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42d0e83ebbc1465181bb94966015fb1c-digital-communications-manager-united-states-of-care-washington</t>
+  </si>
+  <si>
+    <t>Queens College Hillel</t>
+  </si>
+  <si>
+    <t>Queens, New York</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4af668d6e4884a35958bae48b9db3d5c-director-of-advancement-queens-college-hillel-queens</t>
+  </si>
+  <si>
+    <t>Director of Annual Giving Strategy</t>
+  </si>
+  <si>
+    <t>Hopkins School</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/358bda2b5ae64e76b5fe197e27234384-director-of-annual-giving-strategy-hopkins-school-new-haven</t>
+  </si>
+  <si>
+    <t>Director of Development &amp; Communications</t>
+  </si>
+  <si>
+    <t>Row New York</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a81e40585974c08ba28cf903bfae80b-director-of-development-communications-row-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Dog Behavior Specialist</t>
+  </si>
+  <si>
+    <t>Orphans of the Storm</t>
+  </si>
+  <si>
+    <t>Riverwoods, Illinois</t>
+  </si>
+  <si>
+    <t>USD 40000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d9ab3f29115947e0afd35f1049ec3e1e-dog-behavior-specialist-orphans-of-the-storm-riverwoods</t>
+  </si>
+  <si>
+    <t>Education &amp; Career Pathways Manager</t>
+  </si>
+  <si>
+    <t>A Place Called Home</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 31.26 - 33.17/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a42acaf6f73041f5a7de842e21324d7b-education-career-pathways-manager-a-place-called-home-los-angeles</t>
+  </si>
+  <si>
+    <t>Education Program Associate</t>
+  </si>
+  <si>
+    <t>The Right Question Institute</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/98144a23a4dd4b4bb7c8fe7ebedc75a9-education-program-associate-the-right-question-institute-cambridge</t>
+  </si>
+  <si>
+    <t>Employment Specialist</t>
+  </si>
+  <si>
+    <t>CodeSquad</t>
+  </si>
+  <si>
+    <t>Somerville, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 22.00/hour</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49932974ff4f46c9ada62bdf59ade84e-employment-specialist-codesquad-somerville</t>
+  </si>
+  <si>
+    <t>ETSU GLOBAL PRIMARY CARE FELLOWSHIP | Non-ACGME Post-Residency Fellowship</t>
+  </si>
+  <si>
+    <t>Hillside Health Care</t>
+  </si>
+  <si>
+    <t>Eldridgeville, Toledo District, BZ</t>
+  </si>
+  <si>
+    <t>Health Medicine, Women, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fec11929f90d4f95aad1e48056867ae3-etsu-global-primary-care-fellowship-non-acgme-post-residency-fellowship-hillside-health-care-eldridgeville</t>
+  </si>
+  <si>
+    <t>Family Promise of Gwinnett County</t>
+  </si>
+  <si>
+    <t>Lawrenceville, Georgia</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b4ba9ad2f0e483b980f83192adad1f6-executive-director-family-promise-of-gwinnett-county-lawrenceville</t>
+  </si>
+  <si>
+    <t>Castle Square Tenants Organization</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f9d6b07d6771432295ada90f58d6f3ab-executive-director-castle-square-tenants-organization-boston</t>
+  </si>
+  <si>
+    <t>Reclaim Philadelphia</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5ebdbdf95ca947e2a243764ce68ff5df-executive-director-reclaim-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Cystic Fibrosis Foundation - Cff.org</t>
+  </si>
+  <si>
+    <t>West Palm Beach, Florida</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2cf87df6bf7b43cab99e9a8d5d9bd2f6-executive-director-cystic-fibrosis-foundation-cfforg-west-palm-beach</t>
+  </si>
+  <si>
+    <t>Executive Director/Managing Agent, Southwick Housing Authority</t>
+  </si>
+  <si>
+    <t>Massachusetts NAHRO</t>
+  </si>
+  <si>
+    <t>Southwick, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 42951.00 - 47724.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/278f39670292412ea402ff987f137c2b-executive-directormanaging-agent-southwick-housing-authority-massachusetts-nahro-southwick</t>
+  </si>
+  <si>
+    <t>Family Services Worker</t>
+  </si>
+  <si>
+    <t>Children's Learning Centers of Fairfield County</t>
+  </si>
+  <si>
+    <t>Stamford, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3fda5e32a0442bd8087e66b09d37e9f-family-services-worker-childrens-learning-centers-of-fairfield-county-stamford</t>
+  </si>
+  <si>
+    <t>Food Pantry Coordinator</t>
+  </si>
+  <si>
+    <t>Lynwood Partners Educational Foundation</t>
+  </si>
+  <si>
+    <t>Lynwood, California</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20ce0721256947f3a661380c2f5d6d9e-food-pantry-coordinator-lynwood-partners-educational-foundation-lynwood</t>
+  </si>
+  <si>
+    <t>Government Representative 2 – Quantitative Program Evaluator (Job Posting #480-26)</t>
+  </si>
+  <si>
+    <t>New Jersey Department of Children and Families</t>
+  </si>
+  <si>
+    <t>Trenton, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8bafb9ad512d4e8eb95a06b477cf0ac2-government-representative-2-quantitative-program-evaluator-job-posting-480-26-new-jersey-department-of-children-and-families-trenton</t>
+  </si>
+  <si>
+    <t>Housing Attorney – Veterans Advocacy (No eviction defense) (Four-Day Week, Hybrid)</t>
+  </si>
+  <si>
+    <t>Mental Health Advocacy Services, Inc.</t>
+  </si>
+  <si>
+    <t>Glendale, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f32f7190eafc42a091c378434f4d839f-housing-attorney-veterans-advocacy-no-eviction-defense-four-day-week-hybrid-mental-health-advocacy-services-inc-glendale</t>
+  </si>
+  <si>
+    <t>Interdisciplinary AI Project Manager</t>
+  </si>
+  <si>
+    <t>CSTA</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/202ee2e59c694079a509586bf14f2ff2-interdisciplinary-ai-project-manager-csta-chicago</t>
+  </si>
+  <si>
+    <t>Intern, FedEx Corporate Diplomacy</t>
+  </si>
+  <si>
+    <t>Meridian International Center</t>
+  </si>
+  <si>
+    <t>USD 18.40 - 18.40/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4da62704082e47d6816a0bb8d4122508-intern-fedex-corporate-diplomacy-meridian-international-center-washington</t>
+  </si>
+  <si>
+    <t>K-12 Education Mobilization Associate</t>
+  </si>
+  <si>
+    <t>Children First PA</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1521717859a74ff3b550920691793dd5-k-12-education-mobilization-associate-children-first-pa-philadelphia</t>
+  </si>
+  <si>
+    <t>Legal Director</t>
+  </si>
+  <si>
+    <t>Pension Rights Center</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3978a4d80b274ddca449e8dac65c2afe-legal-director-pension-rights-center-washington</t>
+  </si>
+  <si>
+    <t>Manager of Service Corps Partnerships</t>
+  </si>
+  <si>
+    <t>Maryland Alliance of Boys &amp; Girls Clubs</t>
+  </si>
+  <si>
+    <t>Annapolis, Maryland</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c124d652876b41d08fd91ef89279a30c-manager-of-service-corps-partnerships-maryland-alliance-of-boys-girls-clubs-annapolis</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Communications Associate</t>
+  </si>
+  <si>
+    <t>PBLWorks</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/459f4c52f1ef4f09b7d3c85866cf1a4b-marketing-communications-associate-pblworks-novato</t>
+  </si>
+  <si>
+    <t>Membership &amp; Advocacy Coordinator</t>
+  </si>
+  <si>
+    <t>Mass NOW</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Lgbtq, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f722db4f0044dcf80e9264428a2e119-membership-advocacy-coordinator-mass-now-boston</t>
+  </si>
+  <si>
+    <t>Nutrition Program Manager</t>
+  </si>
+  <si>
+    <t>Reinvestment Partners</t>
+  </si>
+  <si>
+    <t>Durham, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0fe35bae9478478ea5ab41b27fd3cf75-nutrition-program-manager-reinvestment-partners-durham</t>
+  </si>
+  <si>
+    <t>Office Manager</t>
+  </si>
+  <si>
+    <t>Hillside, Illinois</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5fd13bc8c5df4d62b1288f856e1f68d8-office-manager-careers-in-nonprofits-inc-hillside</t>
+  </si>
+  <si>
+    <t>Older Adults Food Service Worker (Flatbush YMCA)</t>
+  </si>
+  <si>
+    <t>YMCA of Greater New York</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 18.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/44b3fc30800a420490516017607b7626-older-adults-food-service-worker-flatbush-ymca-ymca-of-greater-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>We Animals</t>
+  </si>
+  <si>
+    <t>Remote (CA)</t>
+  </si>
+  <si>
+    <t>CAD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5aa4b828c7304f8a945572c0f064d6db-operations-manager-we-animals-toronto</t>
+  </si>
+  <si>
+    <t>People Operations Lead</t>
+  </si>
+  <si>
+    <t>Mirror Biology Dialogues Fund</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Science Technology, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b21a9e4414c74f5093d5b48a56ef5ea5-people-operations-lead-mirror-biology-dialogues-fund-new-york</t>
+  </si>
+  <si>
+    <t>Physical Therapist in Belize (Volunteer)</t>
+  </si>
+  <si>
+    <t>USD 16000.00 - 18000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d53bff62c35c4b4fbcd5c96403220004-physical-therapist-in-belize-volunteer-hillside-health-care-eldridgeville</t>
+  </si>
+  <si>
+    <t>Policy Counsel/Senior Policy Counsel - First Amendment/Free Speech/Defensive Work</t>
+  </si>
+  <si>
+    <t>New York Civil Liberties Union Foundation</t>
+  </si>
+  <si>
+    <t>USD 99500.00 - 122500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/e2b92b90e5a64c5082921e3573af4b5a-policy-counselsenior-policy-counsel-first-amendmentfree-speechdefensive-work-new-york-civil-liberties-union-foundation-new-york</t>
+  </si>
+  <si>
+    <t>Prevention Specialist</t>
+  </si>
+  <si>
+    <t>Doorways</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 57000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/caccef4e823f40cd848eba09d53199f3-prevention-specialist-doorways-arlington</t>
+  </si>
+  <si>
+    <t>Principal</t>
+  </si>
+  <si>
+    <t>Pillar Care Continuum</t>
+  </si>
+  <si>
+    <t>Livingston, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/62395cf6d5a44c8199f1d5f57251b45e-principal-pillar-care-continuum-livingston</t>
+  </si>
+  <si>
+    <t>Program Assistant, Africa Program</t>
+  </si>
+  <si>
+    <t>Carnegie Endowment for International Peace</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95ac7f27aa734cf9a00cf423057aa369-program-assistant-africa-program-carnegie-endowment-for-international-peace-washington</t>
+  </si>
+  <si>
+    <t>Program Coordinator, Teacher Professional Development (Full-Time, Three-Year Term)</t>
+  </si>
+  <si>
+    <t>The Gilder Lehrman Institute of American History</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 63500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7cae70645b946ab881e4b7182539acd-program-coordinator-teacher-professional-development-full-time-three-year-term-the-gilder-lehrman-institute-of-american-history-new-york</t>
+  </si>
+  <si>
+    <t>Program Director—College Bound</t>
+  </si>
+  <si>
+    <t>Breakthrough Houston</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 90000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34a01e7b215b4bc991e4732907acf326-program-directorcollege-bound-breakthrough-houston-houston</t>
+  </si>
+  <si>
+    <t>Project Coordinator - Fundraising and Marketing</t>
+  </si>
+  <si>
+    <t>MKDM</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Health Medicine, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/bea6f0f816fd43cf921b6d8b3f04a894-project-coordinator-fundraising-and-marketing-mkdm-atlanta</t>
+  </si>
+  <si>
+    <t>Fredericksburg, Virginia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/ae8bad8de0b04d19874f85b474aa6da5-project-coordinator-fundraising-and-marketing-mkdm-fredericksburg</t>
+  </si>
+  <si>
+    <t>Charlottesville, Virginia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/04c136e4fc0044a680a27f4776f05f01-project-coordinator-fundraising-and-marketing-mkdm-charlottesville</t>
+  </si>
+  <si>
+    <t>Rapid Rehousing Coordinator</t>
+  </si>
+  <si>
+    <t>Carpenter's Shelter</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96dd5006fbb04836a79e3e3985058ecd-rapid-rehousing-coordinator-carpenters-shelter-alexandria</t>
+  </si>
+  <si>
+    <t>REGISTRAR/EDUCATION ASSISTANT</t>
+  </si>
+  <si>
+    <t>Wave Hill (Bronx, New York)</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 46503.00 - 46503.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b640c83be1b450d898e3c033ae613d0-registrareducation-assistant-wave-hill-bronx-new-york-bronx-county</t>
+  </si>
+  <si>
+    <t>Research Development Professional</t>
+  </si>
+  <si>
+    <t>University of Minnesota Research Development Office</t>
+  </si>
+  <si>
+    <t>Duluth, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d914bf1544a40e7910bb5b1fb394d4a-research-development-professional-university-of-minnesota-research-development-office-duluth</t>
+  </si>
+  <si>
+    <t>School Programs Coordinator</t>
+  </si>
+  <si>
+    <t>Bronx, NY</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa4ca54433894f1aafe52fdee651282e-school-programs-coordinator-wave-hill-bronx-new-york-bronx</t>
+  </si>
+  <si>
+    <t>Senior Case Manager</t>
+  </si>
+  <si>
+    <t>Episcopal Community Services of San Francisco</t>
+  </si>
+  <si>
+    <t>South San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a8bd5a3e6f834f78b3ba54b90203256e-senior-case-manager-episcopal-community-services-of-san-francisco-south-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Coordinator, Scratch Cook Programs</t>
+  </si>
+  <si>
+    <t>Chef Ann Foundation</t>
+  </si>
+  <si>
+    <t>USD 56687.00 - 72768.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/8e87b8f824e04a4297ec3b3fd61e604a-senior-coordinator-scratch-cook-programs-chef-ann-foundation-boulder</t>
+  </si>
+  <si>
+    <t>Senior Director of Communications</t>
+  </si>
+  <si>
+    <t>American Business Immigration Coalition</t>
+  </si>
+  <si>
+    <t>USD 185000.00 - 215000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6844aedd743b411fbf0737f3ce826240-senior-director-of-communications-american-business-immigration-coalition-chicago</t>
+  </si>
+  <si>
+    <t>Senior Director of Policy and Government Affairs</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/73dced6cf31f4b7a8d675079b0f76fa4-senior-director-of-policy-and-government-affairs-american-business-immigration-coalition-washington</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney - Immigrant Rights Program</t>
+  </si>
+  <si>
+    <t>Asian American Legal Defense and Education Fund</t>
+  </si>
+  <si>
+    <t>USD 120437.50 - 127437.97/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c47d5517910444db7f543daad20c4fa-senior-staff-attorney-immigrant-rights-program-asian-american-legal-defense-and-education-fund-new-york</t>
+  </si>
+  <si>
+    <t>Seniors Helping Seniors - Help Seniors Stay Home Where They Belong (Beach Cities-South Bay, Torrance, Palos Verdes, San Pedro, El Segundo)</t>
+  </si>
+  <si>
+    <t>Seniors Helping Seniors South Bay</t>
+  </si>
+  <si>
+    <t>Torrance, California</t>
+  </si>
+  <si>
+    <t>USD 20.00/hour</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/b24aa62f95954c68b71f863adca9919e-seniors-helping-seniors-help-seniors-stay-home-where-they-belong-beach-cities-south-bay-torrance-palos-verdes-san-pedro-el-segundo-seniors-helping-seniors-south-bay-torrance</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>New Mexico Wilderness Alliance</t>
+  </si>
+  <si>
+    <t>Albuquerque, New Mexico</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d16410dcd3c43728d5753043ee3b77a-staff-attorney-new-mexico-wilderness-alliance-albuquerque</t>
+  </si>
+  <si>
+    <t>Supervising Attorney - Medical Legal Partnerships</t>
+  </si>
+  <si>
+    <t>Legal Clinic for the Disabled</t>
+  </si>
+  <si>
+    <t>Disability, Legal Assistance, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/032729ccda114c66af6957cd12347940-supervising-attorney-medical-legal-partnerships-legal-clinic-for-the-disabled-philadelphia</t>
+  </si>
+  <si>
+    <t>Supervising Attorney, Community Justice Unit, Red Bank, NJ</t>
+  </si>
+  <si>
+    <t>AFSC (American Friends Service Committee)</t>
+  </si>
+  <si>
+    <t>Red Bank, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 82000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5dc867d68ac2427bb765f972601e4f46-supervising-attorney-community-justice-unit-red-bank-nj-afsc-american-friends-service-committee-red-bank</t>
+  </si>
+  <si>
+    <t>TALLERISTA APOYO ESCOLAR - CENTRO BARRIAL LA LUCILA</t>
+  </si>
+  <si>
+    <t>Villa Lynch, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/a9a44919e2dc4d3ea0ce592cf214e59e-tallerista-apoyo-escolar-centro-barrial-la-lucila-centros-barriales-municipalidad-de-vicente-lopez-villa-lynch</t>
+  </si>
+  <si>
+    <t>TALLERISTA APOYO ESCOLAR - OLIVOS</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/461515670b4e4f6fbf0c403abc883fbf-tallerista-apoyo-escolar-olivos-centros-barriales-municipalidad-de-vicente-lopez-villa-lynch</t>
+  </si>
+  <si>
+    <t>Temporary Freelance Salesforce Data Administrator / Consultant</t>
+  </si>
+  <si>
+    <t>Community-Word Project</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3fd8311922fd4db78a9646335cf2912e-temporary-freelance-salesforce-data-administrator-consultant-community-word-project-new-york</t>
+  </si>
+  <si>
+    <t>Vice President for Ocean Conservation</t>
+  </si>
+  <si>
+    <t>The Conservation Law Foundation</t>
+  </si>
+  <si>
+    <t>Community Development, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7614a192b10340109fbc2c4695ac60b7-vice-president-for-ocean-conservation-the-conservation-law-foundation-boston</t>
+  </si>
+  <si>
+    <t>Vice President of Development</t>
+  </si>
+  <si>
+    <t>Flatbush Cats</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 220000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/609013d2e289401ba1372d9e24ee1c32-vice-president-of-development-flatbush-cats-kings-county</t>
+  </si>
+  <si>
+    <t>Vice President of Marketing and Communications</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eff0718260844af1b050c5dde447d120-vice-president-of-marketing-and-communications-flatbush-cats-kings-county</t>
+  </si>
+  <si>
+    <t>Vice President, Brand &amp; Marketing</t>
+  </si>
+  <si>
+    <t>OneTable</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 195000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e6d53ad84c29402c8cf82d81db33c5b0-vice-president-brand-marketing-onetable-new-york</t>
+  </si>
+  <si>
+    <t>Volunteer Programs Director</t>
+  </si>
+  <si>
+    <t>OMUTUKUVU PROJECT</t>
+  </si>
+  <si>
+    <t>Mayuge, Eastern Region, UG</t>
+  </si>
+  <si>
+    <t>Children Youth, Agriculture, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/01c200c95d2341deab4cd97c60863779-volunteer-programs-director-omutukuvu-project-mayuge</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99d886bcb62a46c38de8086236460411-volunteer-programs-director-omutukuvu-project-mayuge</t>
+  </si>
+  <si>
+    <t>Children Youth, Agriculture, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1f47a8279ec4a9d92059b4215e24c3e-volunteer-programs-director-omutukuvu-project-mayuge</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1770,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1796,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2178,802 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" t="s">
+        <v>105</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" t="s">
+        <v>117</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" t="s">
+        <v>128</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="s">
+        <v>133</v>
+      </c>
+      <c r="F24" t="s">
+        <v>134</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C25" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>139</v>
+      </c>
+      <c r="F25" t="s">
+        <v>140</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>145</v>
+      </c>
+      <c r="F26" t="s">
+        <v>146</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" t="s">
+        <v>151</v>
+      </c>
+      <c r="F27" t="s">
+        <v>152</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" t="s">
+        <v>157</v>
+      </c>
+      <c r="F28" t="s">
+        <v>158</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" t="s">
+        <v>163</v>
+      </c>
+      <c r="F29" t="s">
+        <v>164</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>169</v>
+      </c>
+      <c r="F30" t="s">
+        <v>170</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B31" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" t="s">
+        <v>174</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" t="s">
+        <v>175</v>
+      </c>
+      <c r="F31" t="s">
+        <v>90</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32" t="s">
+        <v>178</v>
+      </c>
+      <c r="C32" t="s">
+        <v>179</v>
+      </c>
+      <c r="D32" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>181</v>
+      </c>
+      <c r="B33" t="s">
+        <v>182</v>
+      </c>
+      <c r="C33" t="s">
+        <v>183</v>
+      </c>
+      <c r="D33" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" t="s">
+        <v>184</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" t="s">
+        <v>182</v>
+      </c>
+      <c r="C34" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>188</v>
+      </c>
+      <c r="F34" t="s">
+        <v>42</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3029,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3068,1906 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E7" t="s">
+        <v>194</v>
+      </c>
+      <c r="F7" t="s">
+        <v>224</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F8" t="s">
+        <v>230</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" t="s">
+        <v>240</v>
+      </c>
+      <c r="F10" t="s">
+        <v>194</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>242</v>
+      </c>
+      <c r="B11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C11" t="s">
+        <v>244</v>
+      </c>
+      <c r="D11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" t="s">
+        <v>246</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>248</v>
+      </c>
+      <c r="B12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" t="s">
+        <v>212</v>
+      </c>
+      <c r="E12" t="s">
+        <v>251</v>
+      </c>
+      <c r="F12" t="s">
+        <v>252</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B13" t="s">
+        <v>255</v>
+      </c>
+      <c r="C13" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" t="s">
+        <v>256</v>
+      </c>
+      <c r="F13" t="s">
+        <v>257</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>259</v>
+      </c>
+      <c r="B14" t="s">
+        <v>260</v>
+      </c>
+      <c r="C14" t="s">
+        <v>261</v>
+      </c>
+      <c r="D14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E14" t="s">
+        <v>262</v>
+      </c>
+      <c r="F14" t="s">
+        <v>263</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>265</v>
+      </c>
+      <c r="B15" t="s">
+        <v>266</v>
+      </c>
+      <c r="C15" t="s">
+        <v>267</v>
+      </c>
+      <c r="D15" t="s">
+        <v>193</v>
+      </c>
+      <c r="E15" t="s">
+        <v>268</v>
+      </c>
+      <c r="F15" t="s">
+        <v>269</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>271</v>
+      </c>
+      <c r="B16" t="s">
+        <v>272</v>
+      </c>
+      <c r="C16" t="s">
+        <v>228</v>
+      </c>
+      <c r="D16" t="s">
+        <v>193</v>
+      </c>
+      <c r="E16" t="s">
+        <v>273</v>
+      </c>
+      <c r="F16" t="s">
+        <v>274</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>276</v>
+      </c>
+      <c r="B17" t="s">
+        <v>277</v>
+      </c>
+      <c r="C17" t="s">
+        <v>278</v>
+      </c>
+      <c r="D17" t="s">
+        <v>193</v>
+      </c>
+      <c r="E17" t="s">
+        <v>279</v>
+      </c>
+      <c r="F17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>282</v>
+      </c>
+      <c r="B18" t="s">
+        <v>283</v>
+      </c>
+      <c r="C18" t="s">
+        <v>211</v>
+      </c>
+      <c r="D18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E18" t="s">
+        <v>284</v>
+      </c>
+      <c r="F18" t="s">
+        <v>285</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" t="s">
+        <v>287</v>
+      </c>
+      <c r="C19" t="s">
+        <v>288</v>
+      </c>
+      <c r="D19" t="s">
+        <v>193</v>
+      </c>
+      <c r="E19" t="s">
+        <v>289</v>
+      </c>
+      <c r="F19" t="s">
+        <v>290</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>292</v>
+      </c>
+      <c r="B20" t="s">
+        <v>293</v>
+      </c>
+      <c r="C20" t="s">
+        <v>294</v>
+      </c>
+      <c r="D20" t="s">
+        <v>193</v>
+      </c>
+      <c r="E20" t="s">
+        <v>295</v>
+      </c>
+      <c r="F20" t="s">
+        <v>296</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>298</v>
+      </c>
+      <c r="B21" t="s">
+        <v>299</v>
+      </c>
+      <c r="C21" t="s">
+        <v>261</v>
+      </c>
+      <c r="D21" t="s">
+        <v>193</v>
+      </c>
+      <c r="E21" t="s">
+        <v>289</v>
+      </c>
+      <c r="F21" t="s">
+        <v>300</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>302</v>
+      </c>
+      <c r="B22" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" t="s">
+        <v>304</v>
+      </c>
+      <c r="D22" t="s">
+        <v>193</v>
+      </c>
+      <c r="E22" t="s">
+        <v>305</v>
+      </c>
+      <c r="F22" t="s">
+        <v>306</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>308</v>
+      </c>
+      <c r="B23" t="s">
+        <v>309</v>
+      </c>
+      <c r="C23" t="s">
+        <v>310</v>
+      </c>
+      <c r="D23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E23" t="s">
+        <v>311</v>
+      </c>
+      <c r="F23" t="s">
+        <v>218</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>313</v>
+      </c>
+      <c r="B24" t="s">
+        <v>314</v>
+      </c>
+      <c r="C24" t="s">
+        <v>211</v>
+      </c>
+      <c r="D24" t="s">
+        <v>193</v>
+      </c>
+      <c r="E24" t="s">
+        <v>315</v>
+      </c>
+      <c r="F24" t="s">
+        <v>316</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>318</v>
+      </c>
+      <c r="B25" t="s">
+        <v>319</v>
+      </c>
+      <c r="C25" t="s">
+        <v>320</v>
+      </c>
+      <c r="D25" t="s">
+        <v>212</v>
+      </c>
+      <c r="E25" t="s">
+        <v>321</v>
+      </c>
+      <c r="F25" t="s">
+        <v>322</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>324</v>
+      </c>
+      <c r="B26" t="s">
+        <v>325</v>
+      </c>
+      <c r="C26" t="s">
+        <v>326</v>
+      </c>
+      <c r="D26" t="s">
+        <v>193</v>
+      </c>
+      <c r="E26" t="s">
+        <v>194</v>
+      </c>
+      <c r="F26" t="s">
+        <v>327</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" t="s">
+        <v>329</v>
+      </c>
+      <c r="C27" t="s">
+        <v>330</v>
+      </c>
+      <c r="D27" t="s">
+        <v>193</v>
+      </c>
+      <c r="E27" t="s">
+        <v>331</v>
+      </c>
+      <c r="F27" t="s">
+        <v>332</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" t="s">
+        <v>334</v>
+      </c>
+      <c r="C28" t="s">
+        <v>335</v>
+      </c>
+      <c r="D28" t="s">
+        <v>193</v>
+      </c>
+      <c r="E28" t="s">
+        <v>336</v>
+      </c>
+      <c r="F28" t="s">
+        <v>337</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" t="s">
+        <v>339</v>
+      </c>
+      <c r="C29" t="s">
+        <v>340</v>
+      </c>
+      <c r="D29" t="s">
+        <v>193</v>
+      </c>
+      <c r="E29" t="s">
+        <v>341</v>
+      </c>
+      <c r="F29" t="s">
+        <v>342</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" t="s">
+        <v>344</v>
+      </c>
+      <c r="C30" t="s">
+        <v>345</v>
+      </c>
+      <c r="D30" t="s">
+        <v>193</v>
+      </c>
+      <c r="E30" t="s">
+        <v>194</v>
+      </c>
+      <c r="F30" t="s">
+        <v>346</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>348</v>
+      </c>
+      <c r="B31" t="s">
+        <v>349</v>
+      </c>
+      <c r="C31" t="s">
+        <v>350</v>
+      </c>
+      <c r="D31" t="s">
+        <v>212</v>
+      </c>
+      <c r="E31" t="s">
+        <v>351</v>
+      </c>
+      <c r="F31" t="s">
+        <v>352</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>354</v>
+      </c>
+      <c r="B32" t="s">
+        <v>355</v>
+      </c>
+      <c r="C32" t="s">
+        <v>356</v>
+      </c>
+      <c r="D32" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32" t="s">
+        <v>357</v>
+      </c>
+      <c r="F32" t="s">
+        <v>358</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>360</v>
+      </c>
+      <c r="B33" t="s">
+        <v>361</v>
+      </c>
+      <c r="C33" t="s">
+        <v>362</v>
+      </c>
+      <c r="D33" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" t="s">
+        <v>363</v>
+      </c>
+      <c r="F33" t="s">
+        <v>358</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>365</v>
+      </c>
+      <c r="B34" t="s">
+        <v>366</v>
+      </c>
+      <c r="C34" t="s">
+        <v>367</v>
+      </c>
+      <c r="D34" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34" t="s">
+        <v>368</v>
+      </c>
+      <c r="F34" t="s">
+        <v>369</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>371</v>
+      </c>
+      <c r="B35" t="s">
+        <v>372</v>
+      </c>
+      <c r="C35" t="s">
+        <v>373</v>
+      </c>
+      <c r="D35" t="s">
+        <v>193</v>
+      </c>
+      <c r="E35" t="s">
+        <v>374</v>
+      </c>
+      <c r="F35" t="s">
+        <v>375</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>377</v>
+      </c>
+      <c r="B36" t="s">
+        <v>378</v>
+      </c>
+      <c r="C36" t="s">
+        <v>211</v>
+      </c>
+      <c r="D36" t="s">
+        <v>193</v>
+      </c>
+      <c r="E36" t="s">
+        <v>194</v>
+      </c>
+      <c r="F36" t="s">
+        <v>194</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>380</v>
+      </c>
+      <c r="B37" t="s">
+        <v>381</v>
+      </c>
+      <c r="C37" t="s">
+        <v>234</v>
+      </c>
+      <c r="D37" t="s">
+        <v>193</v>
+      </c>
+      <c r="E37" t="s">
+        <v>382</v>
+      </c>
+      <c r="F37" t="s">
+        <v>322</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>384</v>
+      </c>
+      <c r="B38" t="s">
+        <v>385</v>
+      </c>
+      <c r="C38" t="s">
+        <v>340</v>
+      </c>
+      <c r="D38" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" t="s">
+        <v>386</v>
+      </c>
+      <c r="F38" t="s">
+        <v>290</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>388</v>
+      </c>
+      <c r="B39" t="s">
+        <v>389</v>
+      </c>
+      <c r="C39" t="s">
+        <v>211</v>
+      </c>
+      <c r="D39" t="s">
+        <v>193</v>
+      </c>
+      <c r="E39" t="s">
+        <v>289</v>
+      </c>
+      <c r="F39" t="s">
+        <v>194</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>391</v>
+      </c>
+      <c r="B40" t="s">
+        <v>392</v>
+      </c>
+      <c r="C40" t="s">
+        <v>393</v>
+      </c>
+      <c r="D40" t="s">
+        <v>193</v>
+      </c>
+      <c r="E40" t="s">
+        <v>394</v>
+      </c>
+      <c r="F40" t="s">
+        <v>395</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>397</v>
+      </c>
+      <c r="B41" t="s">
+        <v>398</v>
+      </c>
+      <c r="C41" t="s">
+        <v>211</v>
+      </c>
+      <c r="D41" t="s">
+        <v>193</v>
+      </c>
+      <c r="E41" t="s">
+        <v>399</v>
+      </c>
+      <c r="F41" t="s">
+        <v>400</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>402</v>
+      </c>
+      <c r="B42" t="s">
+        <v>403</v>
+      </c>
+      <c r="C42" t="s">
+        <v>404</v>
+      </c>
+      <c r="D42" t="s">
+        <v>193</v>
+      </c>
+      <c r="E42" t="s">
+        <v>405</v>
+      </c>
+      <c r="F42" t="s">
+        <v>406</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>408</v>
+      </c>
+      <c r="B43" t="s">
+        <v>409</v>
+      </c>
+      <c r="C43" t="s">
+        <v>410</v>
+      </c>
+      <c r="D43" t="s">
+        <v>193</v>
+      </c>
+      <c r="E43" t="s">
+        <v>411</v>
+      </c>
+      <c r="F43" t="s">
+        <v>412</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>414</v>
+      </c>
+      <c r="B44" t="s">
+        <v>238</v>
+      </c>
+      <c r="C44" t="s">
+        <v>415</v>
+      </c>
+      <c r="D44" t="s">
+        <v>193</v>
+      </c>
+      <c r="E44" t="s">
+        <v>416</v>
+      </c>
+      <c r="F44" t="s">
+        <v>194</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>418</v>
+      </c>
+      <c r="B45" t="s">
+        <v>419</v>
+      </c>
+      <c r="C45" t="s">
+        <v>420</v>
+      </c>
+      <c r="D45" t="s">
+        <v>212</v>
+      </c>
+      <c r="E45" t="s">
+        <v>421</v>
+      </c>
+      <c r="F45" t="s">
+        <v>422</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>424</v>
+      </c>
+      <c r="B46" t="s">
+        <v>425</v>
+      </c>
+      <c r="C46" t="s">
+        <v>426</v>
+      </c>
+      <c r="D46" t="s">
+        <v>193</v>
+      </c>
+      <c r="E46" t="s">
+        <v>427</v>
+      </c>
+      <c r="F46" t="s">
+        <v>428</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>430</v>
+      </c>
+      <c r="B47" t="s">
+        <v>431</v>
+      </c>
+      <c r="C47" t="s">
+        <v>211</v>
+      </c>
+      <c r="D47" t="s">
+        <v>193</v>
+      </c>
+      <c r="E47" t="s">
+        <v>432</v>
+      </c>
+      <c r="F47" t="s">
+        <v>433</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>435</v>
+      </c>
+      <c r="B48" t="s">
+        <v>325</v>
+      </c>
+      <c r="C48" t="s">
+        <v>326</v>
+      </c>
+      <c r="D48" t="s">
+        <v>193</v>
+      </c>
+      <c r="E48" t="s">
+        <v>436</v>
+      </c>
+      <c r="F48" t="s">
+        <v>437</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>439</v>
+      </c>
+      <c r="B49" t="s">
+        <v>440</v>
+      </c>
+      <c r="C49" t="s">
+        <v>261</v>
+      </c>
+      <c r="D49" t="s">
+        <v>193</v>
+      </c>
+      <c r="E49" t="s">
+        <v>441</v>
+      </c>
+      <c r="F49" t="s">
+        <v>194</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>443</v>
+      </c>
+      <c r="B50" t="s">
+        <v>444</v>
+      </c>
+      <c r="C50" t="s">
+        <v>445</v>
+      </c>
+      <c r="D50" t="s">
+        <v>193</v>
+      </c>
+      <c r="E50" t="s">
+        <v>446</v>
+      </c>
+      <c r="F50" t="s">
+        <v>447</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>449</v>
+      </c>
+      <c r="B51" t="s">
+        <v>450</v>
+      </c>
+      <c r="C51" t="s">
+        <v>451</v>
+      </c>
+      <c r="D51" t="s">
+        <v>193</v>
+      </c>
+      <c r="E51" t="s">
+        <v>452</v>
+      </c>
+      <c r="F51" t="s">
+        <v>453</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>455</v>
+      </c>
+      <c r="B52" t="s">
+        <v>456</v>
+      </c>
+      <c r="C52" t="s">
+        <v>138</v>
+      </c>
+      <c r="D52" t="s">
+        <v>193</v>
+      </c>
+      <c r="E52" t="s">
+        <v>457</v>
+      </c>
+      <c r="F52" t="s">
+        <v>458</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>460</v>
+      </c>
+      <c r="B53" t="s">
+        <v>461</v>
+      </c>
+      <c r="C53" t="s">
+        <v>261</v>
+      </c>
+      <c r="D53" t="s">
+        <v>462</v>
+      </c>
+      <c r="E53" t="s">
+        <v>463</v>
+      </c>
+      <c r="F53" t="s">
+        <v>464</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>466</v>
+      </c>
+      <c r="B54" t="s">
+        <v>467</v>
+      </c>
+      <c r="C54" t="s">
+        <v>468</v>
+      </c>
+      <c r="D54" t="s">
+        <v>193</v>
+      </c>
+      <c r="E54" t="s">
+        <v>469</v>
+      </c>
+      <c r="F54" t="s">
+        <v>470</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>472</v>
+      </c>
+      <c r="B55" t="s">
+        <v>473</v>
+      </c>
+      <c r="C55" t="s">
+        <v>474</v>
+      </c>
+      <c r="D55" t="s">
+        <v>193</v>
+      </c>
+      <c r="E55" t="s">
+        <v>475</v>
+      </c>
+      <c r="F55" t="s">
+        <v>476</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>472</v>
+      </c>
+      <c r="B56" t="s">
+        <v>473</v>
+      </c>
+      <c r="C56" t="s">
+        <v>478</v>
+      </c>
+      <c r="D56" t="s">
+        <v>193</v>
+      </c>
+      <c r="E56" t="s">
+        <v>475</v>
+      </c>
+      <c r="F56" t="s">
+        <v>476</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>472</v>
+      </c>
+      <c r="B57" t="s">
+        <v>473</v>
+      </c>
+      <c r="C57" t="s">
+        <v>480</v>
+      </c>
+      <c r="D57" t="s">
+        <v>193</v>
+      </c>
+      <c r="E57" t="s">
+        <v>475</v>
+      </c>
+      <c r="F57" t="s">
+        <v>476</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>482</v>
+      </c>
+      <c r="B58" t="s">
+        <v>483</v>
+      </c>
+      <c r="C58" t="s">
+        <v>484</v>
+      </c>
+      <c r="D58" t="s">
+        <v>193</v>
+      </c>
+      <c r="E58" t="s">
+        <v>485</v>
+      </c>
+      <c r="F58" t="s">
+        <v>486</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>488</v>
+      </c>
+      <c r="B59" t="s">
+        <v>489</v>
+      </c>
+      <c r="C59" t="s">
+        <v>490</v>
+      </c>
+      <c r="D59" t="s">
+        <v>193</v>
+      </c>
+      <c r="E59" t="s">
+        <v>491</v>
+      </c>
+      <c r="F59" t="s">
+        <v>296</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>493</v>
+      </c>
+      <c r="B60" t="s">
+        <v>494</v>
+      </c>
+      <c r="C60" t="s">
+        <v>495</v>
+      </c>
+      <c r="D60" t="s">
+        <v>193</v>
+      </c>
+      <c r="E60" t="s">
+        <v>496</v>
+      </c>
+      <c r="F60" t="s">
+        <v>194</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>498</v>
+      </c>
+      <c r="B61" t="s">
+        <v>489</v>
+      </c>
+      <c r="C61" t="s">
+        <v>499</v>
+      </c>
+      <c r="D61" t="s">
+        <v>193</v>
+      </c>
+      <c r="E61" t="s">
+        <v>500</v>
+      </c>
+      <c r="F61" t="s">
+        <v>274</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>502</v>
+      </c>
+      <c r="B62" t="s">
+        <v>503</v>
+      </c>
+      <c r="C62" t="s">
+        <v>504</v>
+      </c>
+      <c r="D62" t="s">
+        <v>193</v>
+      </c>
+      <c r="E62" t="s">
+        <v>505</v>
+      </c>
+      <c r="F62" t="s">
+        <v>486</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>507</v>
+      </c>
+      <c r="B63" t="s">
+        <v>508</v>
+      </c>
+      <c r="C63" t="s">
+        <v>211</v>
+      </c>
+      <c r="D63" t="s">
+        <v>193</v>
+      </c>
+      <c r="E63" t="s">
+        <v>509</v>
+      </c>
+      <c r="F63" t="s">
+        <v>194</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>511</v>
+      </c>
+      <c r="B64" t="s">
+        <v>512</v>
+      </c>
+      <c r="C64" t="s">
+        <v>211</v>
+      </c>
+      <c r="D64" t="s">
+        <v>193</v>
+      </c>
+      <c r="E64" t="s">
+        <v>513</v>
+      </c>
+      <c r="F64" t="s">
+        <v>514</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>516</v>
+      </c>
+      <c r="B65" t="s">
+        <v>512</v>
+      </c>
+      <c r="C65" t="s">
+        <v>517</v>
+      </c>
+      <c r="D65" t="s">
+        <v>193</v>
+      </c>
+      <c r="E65" t="s">
+        <v>513</v>
+      </c>
+      <c r="F65" t="s">
+        <v>514</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>519</v>
+      </c>
+      <c r="B66" t="s">
+        <v>520</v>
+      </c>
+      <c r="C66" t="s">
+        <v>261</v>
+      </c>
+      <c r="D66" t="s">
+        <v>193</v>
+      </c>
+      <c r="E66" t="s">
+        <v>521</v>
+      </c>
+      <c r="F66" t="s">
+        <v>522</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>524</v>
+      </c>
+      <c r="B67" t="s">
+        <v>525</v>
+      </c>
+      <c r="C67" t="s">
+        <v>526</v>
+      </c>
+      <c r="D67" t="s">
+        <v>212</v>
+      </c>
+      <c r="E67" t="s">
+        <v>527</v>
+      </c>
+      <c r="F67" t="s">
+        <v>528</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>530</v>
+      </c>
+      <c r="B68" t="s">
+        <v>531</v>
+      </c>
+      <c r="C68" t="s">
+        <v>532</v>
+      </c>
+      <c r="D68" t="s">
+        <v>193</v>
+      </c>
+      <c r="E68" t="s">
+        <v>533</v>
+      </c>
+      <c r="F68" t="s">
+        <v>534</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>536</v>
+      </c>
+      <c r="B69" t="s">
+        <v>537</v>
+      </c>
+      <c r="C69" t="s">
+        <v>340</v>
+      </c>
+      <c r="D69" t="s">
+        <v>193</v>
+      </c>
+      <c r="E69" t="s">
+        <v>394</v>
+      </c>
+      <c r="F69" t="s">
+        <v>538</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>540</v>
+      </c>
+      <c r="B70" t="s">
+        <v>541</v>
+      </c>
+      <c r="C70" t="s">
+        <v>542</v>
+      </c>
+      <c r="D70" t="s">
+        <v>193</v>
+      </c>
+      <c r="E70" t="s">
+        <v>543</v>
+      </c>
+      <c r="F70" t="s">
+        <v>544</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>546</v>
+      </c>
+      <c r="B71" t="s">
+        <v>191</v>
+      </c>
+      <c r="C71" t="s">
+        <v>547</v>
+      </c>
+      <c r="D71" t="s">
+        <v>193</v>
+      </c>
+      <c r="E71" t="s">
+        <v>194</v>
+      </c>
+      <c r="F71" t="s">
+        <v>195</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>549</v>
+      </c>
+      <c r="B72" t="s">
+        <v>191</v>
+      </c>
+      <c r="C72" t="s">
+        <v>547</v>
+      </c>
+      <c r="D72" t="s">
+        <v>193</v>
+      </c>
+      <c r="E72" t="s">
+        <v>194</v>
+      </c>
+      <c r="F72" t="s">
+        <v>195</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>551</v>
+      </c>
+      <c r="B73" t="s">
+        <v>552</v>
+      </c>
+      <c r="C73" t="s">
+        <v>553</v>
+      </c>
+      <c r="D73" t="s">
+        <v>223</v>
+      </c>
+      <c r="E73" t="s">
+        <v>554</v>
+      </c>
+      <c r="F73" t="s">
+        <v>555</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>557</v>
+      </c>
+      <c r="B74" t="s">
+        <v>558</v>
+      </c>
+      <c r="C74" t="s">
+        <v>404</v>
+      </c>
+      <c r="D74" t="s">
+        <v>193</v>
+      </c>
+      <c r="E74" t="s">
+        <v>194</v>
+      </c>
+      <c r="F74" t="s">
+        <v>559</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>561</v>
+      </c>
+      <c r="B75" t="s">
+        <v>562</v>
+      </c>
+      <c r="C75" t="s">
+        <v>420</v>
+      </c>
+      <c r="D75" t="s">
+        <v>193</v>
+      </c>
+      <c r="E75" t="s">
+        <v>563</v>
+      </c>
+      <c r="F75" t="s">
+        <v>306</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>565</v>
+      </c>
+      <c r="B76" t="s">
+        <v>562</v>
+      </c>
+      <c r="C76" t="s">
+        <v>420</v>
+      </c>
+      <c r="D76" t="s">
+        <v>193</v>
+      </c>
+      <c r="E76" t="s">
+        <v>563</v>
+      </c>
+      <c r="F76" t="s">
+        <v>306</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>567</v>
+      </c>
+      <c r="B77" t="s">
+        <v>568</v>
+      </c>
+      <c r="C77" t="s">
+        <v>211</v>
+      </c>
+      <c r="D77" t="s">
+        <v>193</v>
+      </c>
+      <c r="E77" t="s">
+        <v>569</v>
+      </c>
+      <c r="F77" t="s">
+        <v>570</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>572</v>
+      </c>
+      <c r="B78" t="s">
+        <v>573</v>
+      </c>
+      <c r="C78" t="s">
+        <v>574</v>
+      </c>
+      <c r="D78" t="s">
+        <v>193</v>
+      </c>
+      <c r="E78" t="s">
+        <v>194</v>
+      </c>
+      <c r="F78" t="s">
+        <v>575</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>572</v>
+      </c>
+      <c r="B79" t="s">
+        <v>573</v>
+      </c>
+      <c r="C79" t="s">
+        <v>574</v>
+      </c>
+      <c r="D79" t="s">
+        <v>193</v>
+      </c>
+      <c r="E79" t="s">
+        <v>194</v>
+      </c>
+      <c r="F79" t="s">
+        <v>575</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>572</v>
+      </c>
+      <c r="B80" t="s">
+        <v>573</v>
+      </c>
+      <c r="C80" t="s">
+        <v>574</v>
+      </c>
+      <c r="D80" t="s">
+        <v>212</v>
+      </c>
+      <c r="E80" t="s">
+        <v>194</v>
+      </c>
+      <c r="F80" t="s">
+        <v>578</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-23.xlsx
+++ b/docs/xlsx/jobs-2026-10-23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="808">
   <si>
     <t>Title</t>
   </si>
@@ -586,6 +586,27 @@
     <t>https://www.conservationjobboard.com/job-listing-visitor-services-assistant-nps-zion-national-park-springdale-utah/2568532072</t>
   </si>
   <si>
+    <t>Aftercare Social Worker</t>
+  </si>
+  <si>
+    <t>Ronald McDonald House Philadelphia</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 61500.00 - 68500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a43e96af5724757bc064fe25204ecaf-aftercare-social-worker-ronald-mcdonald-house-philadelphia-philadelphia</t>
+  </si>
+  <si>
     <t>APOYO ESCOLAR - CENTRO BARRIAL LA LUCILA</t>
   </si>
   <si>
@@ -595,9 +616,6 @@
     <t>Florida, Buenos Aires, AR</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -607,6 +625,33 @@
     <t>https://www.idealist.org/en/government-job/99a10b9e83a545f18a202472342374b5-apoyo-escolar-centro-barrial-la-lucila-centros-barriales-municipalidad-de-vicente-lopez-florida</t>
   </si>
   <si>
+    <t>Assistant Attorney General</t>
+  </si>
+  <si>
+    <t>Office of the Massachusetts Attorney General</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90125.00 - 134513.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/733d44311f474a6f8cb074bf6cd2dc54-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>Assistant Director of Institutional Giving</t>
+  </si>
+  <si>
+    <t>Native Arts and Cultures Foundation</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/cf399fab32ba44b6ba8fb70df874131c-assistant-director-of-institutional-giving-native-arts-and-cultures-foundation-portland</t>
+  </si>
+  <si>
     <t>Associate Community Organizer</t>
   </si>
   <si>
@@ -625,6 +670,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/a7d8ef41d4904a9989b29bc2fab2a6d6-associate-community-organizer-direct-action-research-training-center-kansas-city</t>
   </si>
   <si>
+    <t>Attorney (full-time) at Law Firm Exclusively Serving Nonprofit/Tax-Exempt Organizations</t>
+  </si>
+  <si>
+    <t>Cheshire Law Group</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 45.00 - 55.00/hour</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/a93c8e7ee438408d94276bd79cea83bf-attorney-full-time-at-law-firm-exclusively-serving-nonprofittax-exempt-organizations-cheshire-law-group-philadelphia</t>
+  </si>
+  <si>
+    <t>Attorney (part-time) at Law Firm Exclusively Serving Nonprofit/Tax-Exempt Organizations</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/f27fda31912f433caffa4694fe53015a-attorney-part-time-at-law-firm-exclusively-serving-nonprofittax-exempt-organizations-cheshire-law-group-philadelphia</t>
+  </si>
+  <si>
+    <t>Attorney (Stay Housed LA Clinic) – Eviction Defense Center</t>
+  </si>
+  <si>
+    <t>Legal Aid Foundation of Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 107552.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/808ae60443c34fdebaac7003d09ec813-attorney-stay-housed-la-clinic-eviction-defense-center-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Bilingual Case Manager</t>
   </si>
   <si>
@@ -643,18 +730,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/e7bb25759cb044c4b250d6a14486528d-bilingual-case-manager-liftup-communities-chicago</t>
   </si>
   <si>
+    <t>Business Administrator</t>
+  </si>
+  <si>
+    <t>California Immigration Project</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>USD 37.95 - 47.18/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09e33d78020749878fe4c01a9f65a85e-business-administrator-california-immigration-project-sacramento</t>
+  </si>
+  <si>
     <t>Chapter and Walk Manager - Western Region</t>
   </si>
   <si>
     <t>Cure JM Foundation</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 0.00 - 30000.00/year</t>
   </si>
   <si>
@@ -664,6 +763,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/19005619b9a54b9397997408390a6a2c-chapter-and-walk-manager-western-region-cure-jm-foundation-leesburg</t>
   </si>
   <si>
+    <t>Chief Of Staff</t>
+  </si>
+  <si>
+    <t>Razom, Inc.</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b13b310454f6448487c18d9d675b4c60-chief-of-staff-razom-inc-new-york</t>
+  </si>
+  <si>
     <t>Chief of Staff to the CEO</t>
   </si>
   <si>
@@ -676,6 +793,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/dab74d3c44014dc0935636fec454c9f9-chief-of-staff-to-the-ceo-partners-for-rural-impact-berea</t>
   </si>
   <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>YouthBeat</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53012932ac9c4382a411c4a7070ed1c8-chief-operating-officer-youthbeat-oakland</t>
+  </si>
+  <si>
+    <t>Clark County Regional Organizer</t>
+  </si>
+  <si>
+    <t>OneAmerica</t>
+  </si>
+  <si>
+    <t>Vancouver, Washington</t>
+  </si>
+  <si>
+    <t>USD 61000.00 - 64000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b4a8a7d497b442b9e79efb3f2ca31c5-clark-county-regional-organizer-oneamerica-vancouver</t>
+  </si>
+  <si>
     <t>Clinical Director</t>
   </si>
   <si>
@@ -694,6 +847,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/1f642c4c358141609f3a28fb6810c4cf-clinical-director-neotree-london</t>
   </si>
   <si>
+    <t>Communications and Philanthropy Coordinator</t>
+  </si>
+  <si>
+    <t>Neighborhood Health</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 29.00 - 36.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ccd265357a1941c69d10644c4d1f44b7-communications-and-philanthropy-coordinator-neighborhood-health-alexandria</t>
+  </si>
+  <si>
+    <t>Communications Assistant</t>
+  </si>
+  <si>
+    <t>Pike Animal Welfare Shelter</t>
+  </si>
+  <si>
+    <t>USD 14.00 - 16.00/hour</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35fa60bd4a934e06996f309edee2ef98-communications-assistant-pike-animal-welfare-shelter-petersburg</t>
+  </si>
+  <si>
+    <t>Communications Support Specialist</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/55a688c634344c7792adf57891e2e699-communications-support-specialist-cheshire-law-group-philadelphia</t>
+  </si>
+  <si>
+    <t>Community Market Coordinator</t>
+  </si>
+  <si>
+    <t>Ballard Food Bank</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 40.66 - 40.66/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f29edd241b7546ccb96d04beea1d487e-community-market-coordinator-ballard-food-bank-seattle</t>
+  </si>
+  <si>
     <t>Contracts Manager</t>
   </si>
   <si>
@@ -712,6 +925,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/838f34d33a6c4a58bb6a65a76ae60801-contracts-manager-cai-new-york</t>
   </si>
   <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Southwestern Oregon Workforce Investment Board</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e901029b7d4748ba88b54f651b132466-controller-southwestern-oregon-workforce-investment-board-coos-bay</t>
+  </si>
+  <si>
+    <t>COORDINACIÓN HOSPITALARIA JALTENANGO</t>
+  </si>
+  <si>
+    <t>Compañeros En Salud</t>
+  </si>
+  <si>
+    <t>Ángel Albino Corzo, Chiapas, MX</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>MXN 26250.00 - 26250.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/39fcafc4b2ac45bbb7af53084d82123d-coordinacion-hospitalaria-jaltenango-companeros-en-salud-angel-albino-corzo</t>
+  </si>
+  <si>
     <t>Deputy Director of Communications</t>
   </si>
   <si>
@@ -742,6 +991,21 @@
     <t>https://www.idealist.org/en/job/454b910acc0d4ca69f5e4faaaacf315b-development-events-associate-careers-in-nonprofits-inc-washington</t>
   </si>
   <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>New Horizons Ministries</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 28.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/46025d6a580a4ce8ad8c03eafd243ebc-development-associate-new-horizons-ministries-seattle</t>
+  </si>
+  <si>
     <t>Development Consultant</t>
   </si>
   <si>
@@ -754,9 +1018,6 @@
     <t>USD 50.00 - 50.00/hour</t>
   </si>
   <si>
-    <t>Children Youth, Family, Health Medicine</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/6c0163dec4d14003936d152fd2def52f-development-consultant-mengo-hospital-partners-dallas</t>
   </si>
   <si>
@@ -766,9 +1027,6 @@
     <t>Seattle Out &amp; Proud</t>
   </si>
   <si>
-    <t>Seattle, Washington</t>
-  </si>
-  <si>
     <t>USD 33.00 - 38.00/hour</t>
   </si>
   <si>
@@ -799,9 +1057,6 @@
     <t>Kehilat Romemu</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 90000.00 - 150000.00/year</t>
   </si>
   <si>
@@ -817,9 +1072,6 @@
     <t>My Voice Music</t>
   </si>
   <si>
-    <t>Portland, Oregon</t>
-  </si>
-  <si>
     <t>USD 75000.00 - 75000.00/year</t>
   </si>
   <si>
@@ -829,6 +1081,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/ce9d3202b05d4cbca316dd9ae126c8b0-development-manager-my-voice-music-portland</t>
   </si>
   <si>
+    <t>ChangeLab Solutions</t>
+  </si>
+  <si>
+    <t>USD 97500.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/06b172c2e6af44faae9a34246d7c6113-development-manager-changelab-solutions-oakland</t>
+  </si>
+  <si>
     <t>Development Operations and Donor Engagement Manager</t>
   </si>
   <si>
@@ -892,6 +1156,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/4af668d6e4884a35958bae48b9db3d5c-director-of-advancement-queens-college-hillel-queens</t>
   </si>
   <si>
+    <t>Family Tree Clinic</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 87000.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Lgbtq, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/823f9474152f4f6da5afd1c5018775ab-director-of-advancement-family-tree-clinic-minneapolis</t>
+  </si>
+  <si>
+    <t>Queens Hillel</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4af668d6e4884a35958bae48b9db3d5c-director-of-advancement-queens-hillel-queens</t>
+  </si>
+  <si>
     <t>Director of Annual Giving Strategy</t>
   </si>
   <si>
@@ -922,6 +1207,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/3a81e40585974c08ba28cf903bfae80b-director-of-development-communications-row-new-york-new-york</t>
   </si>
   <si>
+    <t>Director of Programs &amp; Clinical Services</t>
+  </si>
+  <si>
+    <t>Hospice of Santa Barbara</t>
+  </si>
+  <si>
+    <t>Santa Barbara, CA</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b0299c31d1042afa92ee325b5de9b73-director-of-programs-clinical-services-hospice-of-santa-barbara-santa-barbara</t>
+  </si>
+  <si>
+    <t>Director of Strategic Partnerships</t>
+  </si>
+  <si>
+    <t>The Max Foundation</t>
+  </si>
+  <si>
+    <t>USD 134475.00 - 161370.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3792321ce5954975b58a508fa471d560-director-of-strategic-partnerships-the-max-foundation-seattle</t>
+  </si>
+  <si>
     <t>Dog Behavior Specialist</t>
   </si>
   <si>
@@ -934,9 +1249,6 @@
     <t>USD 40000.00/year</t>
   </si>
   <si>
-    <t>Animals</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d9ab3f29115947e0afd35f1049ec3e1e-dog-behavior-specialist-orphans-of-the-storm-riverwoods</t>
   </si>
   <si>
@@ -982,9 +1294,6 @@
     <t>USD 22.00/hour</t>
   </si>
   <si>
-    <t>Job Workplace</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/49932974ff4f46c9ada62bdf59ade84e-employment-specialist-codesquad-somerville</t>
   </si>
   <si>
@@ -1036,9 +1345,6 @@
     <t>Reclaim Philadelphia</t>
   </si>
   <si>
-    <t>Philadelphia, Pennsylvania</t>
-  </si>
-  <si>
     <t>USD 85000.00 - 100000.00/year</t>
   </si>
   <si>
@@ -1054,12 +1360,21 @@
     <t>West Palm Beach, Florida</t>
   </si>
   <si>
-    <t>Health Medicine</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/2cf87df6bf7b43cab99e9a8d5d9bd2f6-executive-director-cystic-fibrosis-foundation-cfforg-west-palm-beach</t>
   </si>
   <si>
+    <t>Builders Beyond Borders</t>
+  </si>
+  <si>
+    <t>Norwalk, Connecticut</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/31ab478399f341c18d3722e0024fff86-executive-director-builders-beyond-borders-norwalk</t>
+  </si>
+  <si>
     <t>Executive Director/Managing Agent, Southwick Housing Authority</t>
   </si>
   <si>
@@ -1078,6 +1393,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/278f39670292412ea402ff987f137c2b-executive-directormanaging-agent-southwick-housing-authority-massachusetts-nahro-southwick</t>
   </si>
   <si>
+    <t>Family Leadership Outreach &amp; Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>CL Strategic</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 28.37 - 28.37/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Mental Health, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/6cbcd64ac6a344aa9e164b4133dbfc35-family-leadership-outreach-engagement-coordinator-cl-strategic-tacoma</t>
+  </si>
+  <si>
+    <t>Family Services Coordinator</t>
+  </si>
+  <si>
+    <t>USD 55750.00 - 59750.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Travel Hospitality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13ebac340e7e45758281ee3f919af365-family-services-coordinator-ronald-mcdonald-house-philadelphia-philadelphia</t>
+  </si>
+  <si>
     <t>Family Services Worker</t>
   </si>
   <si>
@@ -1111,6 +1456,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/20ce0721256947f3a661380c2f5d6d9e-food-pantry-coordinator-lynwood-partners-educational-foundation-lynwood</t>
   </si>
   <si>
+    <t>Gift Administration Coordinator</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a7b33e105b5f420393dcee017f4f1fd2-gift-administration-coordinator-the-choice-inc-washington</t>
+  </si>
+  <si>
     <t>Government Representative 2 – Quantitative Program Evaluator (Job Posting #480-26)</t>
   </si>
   <si>
@@ -1129,6 +1486,51 @@
     <t>https://www.idealist.org/en/job/8bafb9ad512d4e8eb95a06b477cf0ac2-government-representative-2-quantitative-program-evaluator-job-posting-480-26-new-jersey-department-of-children-and-families-trenton</t>
   </si>
   <si>
+    <t>Grant Coordinator, Braver Politics</t>
+  </si>
+  <si>
+    <t>Braver Angels</t>
+  </si>
+  <si>
+    <t>Remote (Utah)</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72c1b22d1c1545a7b23a1f00eef063b3-grant-coordinator-braver-politics-braver-angels-new-york</t>
+  </si>
+  <si>
+    <t>Head of Philanthropy</t>
+  </si>
+  <si>
+    <t>Common Sense Media</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 176000.00 - 209000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/74456804a0584733931bd10c74ebd536-head-of-philanthropy-common-sense-media-san-francisco</t>
+  </si>
+  <si>
+    <t>Health Justice Graduate Intern</t>
+  </si>
+  <si>
+    <t>National Partnership for Women &amp; Families</t>
+  </si>
+  <si>
+    <t>USD 18.40 - 18.40/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/34aad07f679b4819a346a67845dd683f-health-justice-graduate-intern-national-partnership-for-women-families-washington</t>
+  </si>
+  <si>
     <t>Housing Attorney – Veterans Advocacy (No eviction defense) (Four-Day Week, Hybrid)</t>
   </si>
   <si>
@@ -1147,6 +1549,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/f32f7190eafc42a091c378434f4d839f-housing-attorney-veterans-advocacy-no-eviction-defense-four-day-week-hybrid-mental-health-advocacy-services-inc-glendale</t>
   </si>
   <si>
+    <t>HR Adminsitrative Coordinator</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Policy, Civic Engagement, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a60dbbf8a6e44895868f2b80cf35963c-hr-adminsitrative-coordinator-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Immigration Attorney, Detained Removal Defense</t>
+  </si>
+  <si>
+    <t>Brooklyn Defender Services</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 97000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f04b04d49dba4cd1b6b8c39e47764f0e-immigration-attorney-detained-removal-defense-brooklyn-defender-services-brooklyn</t>
+  </si>
+  <si>
+    <t>Immigration Removal Defense Attorney (Staff or Senior Staff)</t>
+  </si>
+  <si>
+    <t>La Raza Centro Legal, Inc</t>
+  </si>
+  <si>
+    <t>San Francisco, CA</t>
+  </si>
+  <si>
+    <t>USD 106700.00 - 116700.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b0ae871faec04e4a893b9d074bb29953-immigration-removal-defense-attorney-staff-or-senior-staff-la-raza-centro-legal-inc-san-francisco</t>
+  </si>
+  <si>
     <t>Interdisciplinary AI Project Manager</t>
   </si>
   <si>
@@ -1162,9 +1612,6 @@
     <t>Meridian International Center</t>
   </si>
   <si>
-    <t>USD 18.40 - 18.40/hour</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/job/4da62704082e47d6816a0bb8d4122508-intern-fedex-corporate-diplomacy-meridian-international-center-washington</t>
   </si>
   <si>
@@ -1189,6 +1636,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/3978a4d80b274ddca449e8dac65c2afe-legal-director-pension-rights-center-washington</t>
   </si>
   <si>
+    <t>Litigation Staff Attorney</t>
+  </si>
+  <si>
+    <t>Eviction Defense Collaborative</t>
+  </si>
+  <si>
+    <t>USD 83000.00 - 93500.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af41fb9af9674de6ad180e2c5ef108ef-litigation-staff-attorney-eviction-defense-collaborative-san-francisco</t>
+  </si>
+  <si>
     <t>Manager of Service Corps Partnerships</t>
   </si>
   <si>
@@ -1207,6 +1669,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/c124d652876b41d08fd91ef89279a30c-manager-of-service-corps-partnerships-maryland-alliance-of-boys-girls-clubs-annapolis</t>
   </si>
   <si>
+    <t>Manager, Behavioral Health Services - Stonewall</t>
+  </si>
+  <si>
+    <t>San Francisco AIDS Foundation</t>
+  </si>
+  <si>
+    <t>Health Medicine, Lgbtq, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/405da6aa326c428d9ed7e68febbb2d5a-manager-behavioral-health-services-stonewall-san-francisco-aids-foundation-san-francisco</t>
+  </si>
+  <si>
     <t>Marketing &amp; Communications Associate</t>
   </si>
   <si>
@@ -1228,9 +1702,6 @@
     <t>Mass NOW</t>
   </si>
   <si>
-    <t>Boston, Massachusetts</t>
-  </si>
-  <si>
     <t>USD 55000.00 - 60000.00/year</t>
   </si>
   <si>
@@ -1240,6 +1711,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/1f722db4f0044dcf80e9264428a2e119-membership-advocacy-coordinator-mass-now-boston</t>
   </si>
   <si>
+    <t>Nonprofit Engagement &amp; Capacity Building Manager</t>
+  </si>
+  <si>
+    <t>Brooklyn Org</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/17b29680b7bc4c09a81237ba235725e4-nonprofit-engagement-capacity-building-manager-brooklyn-org-kings-county</t>
+  </si>
+  <si>
     <t>Nutrition Program Manager</t>
   </si>
   <si>
@@ -1276,9 +1762,6 @@
     <t>YMCA of Greater New York</t>
   </si>
   <si>
-    <t>Kings County, New York</t>
-  </si>
-  <si>
     <t>USD 18.00 - 18.00/hour</t>
   </si>
   <si>
@@ -1306,6 +1789,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/5aa4b828c7304f8a945572c0f064d6db-operations-manager-we-animals-toronto</t>
   </si>
   <si>
+    <t>People Coordinator</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 34.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c68463ab8f8045088d0589d491b284dc-people-coordinator-ronald-mcdonald-house-philadelphia-philadelphia</t>
+  </si>
+  <si>
     <t>People Operations Lead</t>
   </si>
   <si>
@@ -1345,6 +1837,24 @@
     <t>https://www.idealist.org/en/job/e2b92b90e5a64c5082921e3573af4b5a-policy-counselsenior-policy-counsel-first-amendmentfree-speechdefensive-work-new-york-civil-liberties-union-foundation-new-york</t>
   </si>
   <si>
+    <t>Prevention Services Coordinator - Bilingual (Spanish)</t>
+  </si>
+  <si>
+    <t>Long Island Crisis Center</t>
+  </si>
+  <si>
+    <t>Deer Park, New York</t>
+  </si>
+  <si>
+    <t>USD 47000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Lgbtq, Mental Health, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8fcd281d725d42fa84c16f9b7593af66-prevention-services-coordinator-bilingual-spanish-long-island-crisis-center-deer-park</t>
+  </si>
+  <si>
     <t>Prevention Specialist</t>
   </si>
   <si>
@@ -1381,6 +1891,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/62395cf6d5a44c8199f1d5f57251b45e-principal-pillar-care-continuum-livingston</t>
   </si>
   <si>
+    <t>Procurement Secretary</t>
+  </si>
+  <si>
+    <t>Bard Early Colleges</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 46000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/93276c67811a48468476a180452b33f0-procurement-secretary-bard-early-colleges-bronx-county</t>
+  </si>
+  <si>
     <t>Program Assistant, Africa Program</t>
   </si>
   <si>
@@ -1402,9 +1927,6 @@
     <t>The Gilder Lehrman Institute of American History</t>
   </si>
   <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 55000.00 - 63500.00/year</t>
   </si>
   <si>
@@ -1432,6 +1954,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/34a01e7b215b4bc991e4732907acf326-program-directorcollege-bound-breakthrough-houston-houston</t>
   </si>
   <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>Girls on the Run of the Bay Area</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f15e2a3b57e40939c53f99db9fa87f0-program-manager-girls-on-the-run-of-the-bay-area-san-francisco</t>
+  </si>
+  <si>
+    <t>Programs Manager</t>
+  </si>
+  <si>
+    <t>AIA Seattle</t>
+  </si>
+  <si>
+    <t>USD 31.76 - 40.38/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/621263a113a44c4f816b6298a61ae098-programs-manager-aia-seattle-seattle</t>
+  </si>
+  <si>
     <t>Project Coordinator - Fundraising and Marketing</t>
   </si>
   <si>
@@ -1468,9 +2017,6 @@
     <t>Carpenter's Shelter</t>
   </si>
   <si>
-    <t>Alexandria, Virginia</t>
-  </si>
-  <si>
     <t>USD 65000.00 - 72000.00/year</t>
   </si>
   <si>
@@ -1486,9 +2032,6 @@
     <t>Wave Hill (Bronx, New York)</t>
   </si>
   <si>
-    <t>Bronx County, New York</t>
-  </si>
-  <si>
     <t>USD 46503.00 - 46503.00/year</t>
   </si>
   <si>
@@ -1510,6 +2053,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/8d914bf1544a40e7910bb5b1fb394d4a-research-development-professional-university-of-minnesota-research-development-office-duluth</t>
   </si>
   <si>
+    <t>RTC Clinic Legal Supervisor</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e817ab11df854a43878ca13a39cd27a1-rtc-clinic-legal-supervisor-eviction-defense-collaborative-san-francisco</t>
+  </si>
+  <si>
     <t>School Programs Coordinator</t>
   </si>
   <si>
@@ -1522,6 +2074,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/fa4ca54433894f1aafe52fdee651282e-school-programs-coordinator-wave-hill-bronx-new-york-bronx</t>
   </si>
   <si>
+    <t>Seasonal Natural Resources Technician I</t>
+  </si>
+  <si>
+    <t>Santa Clara Valley Open Space Authority</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>USD 40.46 - 40.46/hour</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/0de4af9e8234489f9ed31303e9424e3f-seasonal-natural-resources-technician-i-santa-clara-valley-open-space-authority-san-jose</t>
+  </si>
+  <si>
     <t>Senior Case Manager</t>
   </si>
   <si>
@@ -1537,6 +2107,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/a8bd5a3e6f834f78b3ba54b90203256e-senior-case-manager-episcopal-community-services-of-san-francisco-south-san-francisco</t>
   </si>
   <si>
+    <t>Senior Consultant (Grant Writer, Foundation Relations, Institutional Giving)</t>
+  </si>
+  <si>
+    <t>CIMA Consulting</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 87500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/c6ccec90620148dca8521eb712326284-senior-consultant-grant-writer-foundation-relations-institutional-giving-cima-consulting-charlottesville</t>
+  </si>
+  <si>
     <t>Senior Coordinator, Scratch Cook Programs</t>
   </si>
   <si>
@@ -1549,6 +2131,21 @@
     <t>https://www.idealist.org/en/job/8e87b8f824e04a4297ec3b3fd61e604a-senior-coordinator-scratch-cook-programs-chef-ann-foundation-boulder</t>
   </si>
   <si>
+    <t>Senior Development and Communications Specialist</t>
+  </si>
+  <si>
+    <t>Jones Valley Teaching Farm</t>
+  </si>
+  <si>
+    <t>Birmingham, Alabama</t>
+  </si>
+  <si>
+    <t>Agriculture, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eefd34fb13c649968d0522af3b6fad69-senior-development-and-communications-specialist-jones-valley-teaching-farm-birmingham</t>
+  </si>
+  <si>
     <t>Senior Director of Communications</t>
   </si>
   <si>
@@ -1573,6 +2170,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/73dced6cf31f4b7a8d675079b0f76fa4-senior-director-of-policy-and-government-affairs-american-business-immigration-coalition-washington</t>
   </si>
   <si>
+    <t>Senior Grant Writer</t>
+  </si>
+  <si>
+    <t>Institute for Nonprofit Practice</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae977e7c50f2467eb39adc294a9e7660-senior-grant-writer-institute-for-nonprofit-practice-boston</t>
+  </si>
+  <si>
+    <t>Senior Policy Manager</t>
+  </si>
+  <si>
+    <t>USD 82000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Policy, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e270a8ebc925486d8cfacb312caad512-senior-policy-manager-oneamerica-seattle</t>
+  </si>
+  <si>
     <t>Senior Staff Attorney - Immigrant Rights Program</t>
   </si>
   <si>
@@ -1582,9 +2206,6 @@
     <t>USD 120437.50 - 127437.97/year</t>
   </si>
   <si>
-    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Legal Assistance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/5c47d5517910444db7f543daad20c4fa-senior-staff-attorney-immigrant-rights-program-asian-american-legal-defense-and-education-fund-new-york</t>
   </si>
   <si>
@@ -1606,6 +2227,21 @@
     <t>https://www.idealist.org/en/business-job/b24aa62f95954c68b71f863adca9919e-seniors-helping-seniors-help-seniors-stay-home-where-they-belong-beach-cities-south-bay-torrance-palos-verdes-san-pedro-el-segundo-seniors-helping-seniors-south-bay-torrance</t>
   </si>
   <si>
+    <t>Sierra Watch Field Organizer</t>
+  </si>
+  <si>
+    <t>Sierra Watch</t>
+  </si>
+  <si>
+    <t>Truckee, California</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e64bfc10a4342b0b934949d9df49bcd-sierra-watch-field-organizer-sierra-watch-truckee</t>
+  </si>
+  <si>
     <t>Staff Attorney</t>
   </si>
   <si>
@@ -1615,9 +2251,6 @@
     <t>Albuquerque, New Mexico</t>
   </si>
   <si>
-    <t>USD 80000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>Environment, Legal Assistance</t>
   </si>
   <si>
@@ -1648,12 +2281,30 @@
     <t>USD 82000.00/year</t>
   </si>
   <si>
-    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/5dc867d68ac2427bb765f972601e4f46-supervising-attorney-community-justice-unit-red-bank-nj-afsc-american-friends-service-committee-red-bank</t>
   </si>
   <si>
+    <t>Supervising Attorney, Detention and Deportation Defense Initiative</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e309300a8c343dd92637455c51fb1a2-supervising-attorney-detention-and-deportation-defense-initiative-afsc-american-friends-service-committee-newark</t>
+  </si>
+  <si>
+    <t>Supportive Services for Veteran Families(SSVF) Case Manager</t>
+  </si>
+  <si>
+    <t>Everyone Home DC</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f9e56874a6e49e98f2e0bf4ba18e092-supportive-services-for-veteran-familiesssvf-case-manager-everyone-home-dc-washington</t>
+  </si>
+  <si>
     <t>TALLERISTA APOYO ESCOLAR - CENTRO BARRIAL LA LUCILA</t>
   </si>
   <si>
@@ -1687,6 +2338,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/3fd8311922fd4db78a9646335cf2912e-temporary-freelance-salesforce-data-administrator-consultant-community-word-project-new-york</t>
   </si>
   <si>
+    <t>The Committee for the First Amendment: Video &amp; Content Editor (LA, temp contract)</t>
+  </si>
+  <si>
+    <t>The Committee for the First Amendment</t>
+  </si>
+  <si>
+    <t>Remote (Los Angeles, California)</t>
+  </si>
+  <si>
+    <t>USD 4000.00 - 4000.00/month</t>
+  </si>
+  <si>
+    <t>Arts Music, Media, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2a9d1f5026d4f9cad75197dc93e6e8d-the-committee-for-the-first-amendment-video-content-editor-la-temp-contract-the-committee-for-the-first-amendment-los-angeles</t>
+  </si>
+  <si>
     <t>Vice President for Ocean Conservation</t>
   </si>
   <si>
@@ -1730,6 +2399,21 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/e6d53ad84c29402c8cf82d81db33c5b0-vice-president-brand-marketing-onetable-new-york</t>
+  </si>
+  <si>
+    <t>Volunteer Manager</t>
+  </si>
+  <si>
+    <t>Cascade Bicycle Club</t>
+  </si>
+  <si>
+    <t>USD 70762.00 - 106143.00/year</t>
+  </si>
+  <si>
+    <t>Transportation, Sports Recreation, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a24ccc67652a4f8fbe270f010bd7bb80-volunteer-manager-cascade-bicycle-club-seattle</t>
   </si>
   <si>
     <t>Volunteer Programs Director</t>
@@ -3029,7 +3713,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3131,1758 +3815,2931 @@
         <v>206</v>
       </c>
       <c r="F4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" t="s">
         <v>209</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>210</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F5" t="s">
+        <v>200</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="D5" t="s">
-        <v>212</v>
-      </c>
-      <c r="E5" t="s">
-        <v>213</v>
-      </c>
-      <c r="F5" t="s">
-        <v>214</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F6" t="s">
         <v>216</v>
       </c>
-      <c r="B6" t="s">
+      <c r="H6" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="C6" t="s">
-        <v>211</v>
-      </c>
-      <c r="D6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E6" t="s">
-        <v>194</v>
-      </c>
-      <c r="F6" t="s">
-        <v>218</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" t="s">
         <v>220</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E7" t="s">
         <v>221</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
         <v>222</v>
       </c>
-      <c r="D7" t="s">
+      <c r="H7" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="E7" t="s">
-        <v>194</v>
-      </c>
-      <c r="F7" t="s">
-        <v>224</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" t="s">
+        <v>221</v>
+      </c>
+      <c r="F8" t="s">
+        <v>222</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="B8" t="s">
-        <v>227</v>
-      </c>
-      <c r="C8" t="s">
-        <v>228</v>
-      </c>
-      <c r="D8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" t="s">
-        <v>229</v>
-      </c>
-      <c r="F8" t="s">
-        <v>230</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B9" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D9" t="s">
         <v>193</v>
       </c>
       <c r="E9" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F9" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B10" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C10" t="s">
         <v>234</v>
       </c>
       <c r="D10" t="s">
-        <v>239</v>
+        <v>193</v>
       </c>
       <c r="E10" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F10" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" t="s">
+        <v>241</v>
+      </c>
+      <c r="F11" t="s">
         <v>242</v>
       </c>
-      <c r="B11" t="s">
+      <c r="H11" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C11" t="s">
-        <v>244</v>
-      </c>
-      <c r="D11" t="s">
-        <v>223</v>
-      </c>
-      <c r="E11" t="s">
-        <v>245</v>
-      </c>
-      <c r="F11" t="s">
-        <v>246</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D12" t="s">
+        <v>225</v>
+      </c>
+      <c r="E12" t="s">
+        <v>246</v>
+      </c>
+      <c r="F12" t="s">
+        <v>247</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="B12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C12" t="s">
-        <v>250</v>
-      </c>
-      <c r="D12" t="s">
-        <v>212</v>
-      </c>
-      <c r="E12" t="s">
-        <v>251</v>
-      </c>
-      <c r="F12" t="s">
-        <v>252</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" t="s">
+        <v>251</v>
+      </c>
+      <c r="D13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" t="s">
+        <v>252</v>
+      </c>
+      <c r="F13" t="s">
+        <v>253</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="B13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C13" t="s">
-        <v>211</v>
-      </c>
-      <c r="D13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E13" t="s">
-        <v>256</v>
-      </c>
-      <c r="F13" t="s">
-        <v>257</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B14" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="D14" t="s">
         <v>193</v>
       </c>
       <c r="E14" t="s">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="F14" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B15" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C15" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>193</v>
       </c>
       <c r="E15" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="F15" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B16" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C16" t="s">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="D16" t="s">
         <v>193</v>
       </c>
       <c r="E16" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F16" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>271</v>
+      </c>
+      <c r="B17" t="s">
+        <v>272</v>
+      </c>
+      <c r="C17" t="s">
+        <v>273</v>
+      </c>
+      <c r="D17" t="s">
+        <v>274</v>
+      </c>
+      <c r="E17" t="s">
+        <v>200</v>
+      </c>
+      <c r="F17" t="s">
+        <v>275</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="B17" t="s">
-        <v>277</v>
-      </c>
-      <c r="C17" t="s">
-        <v>278</v>
-      </c>
-      <c r="D17" t="s">
-        <v>193</v>
-      </c>
-      <c r="E17" t="s">
-        <v>279</v>
-      </c>
-      <c r="F17" t="s">
-        <v>280</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>277</v>
+      </c>
+      <c r="B18" t="s">
+        <v>278</v>
+      </c>
+      <c r="C18" t="s">
+        <v>279</v>
+      </c>
+      <c r="D18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E18" t="s">
+        <v>280</v>
+      </c>
+      <c r="F18" t="s">
+        <v>281</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="B18" t="s">
-        <v>283</v>
-      </c>
-      <c r="C18" t="s">
-        <v>211</v>
-      </c>
-      <c r="D18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E18" t="s">
-        <v>284</v>
-      </c>
-      <c r="F18" t="s">
-        <v>285</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>283</v>
       </c>
       <c r="B19" t="s">
+        <v>284</v>
+      </c>
+      <c r="C19" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" t="s">
+        <v>193</v>
+      </c>
+      <c r="E19" t="s">
+        <v>285</v>
+      </c>
+      <c r="F19" t="s">
+        <v>286</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="C19" t="s">
-        <v>288</v>
-      </c>
-      <c r="D19" t="s">
-        <v>193</v>
-      </c>
-      <c r="E19" t="s">
-        <v>289</v>
-      </c>
-      <c r="F19" t="s">
-        <v>290</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B20" t="s">
-        <v>293</v>
+        <v>219</v>
       </c>
       <c r="C20" t="s">
-        <v>294</v>
+        <v>192</v>
       </c>
       <c r="D20" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="E20" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="F20" t="s">
-        <v>296</v>
+        <v>222</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B21" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C21" t="s">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="D21" t="s">
         <v>193</v>
       </c>
       <c r="E21" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F21" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>297</v>
+      </c>
+      <c r="B22" t="s">
+        <v>298</v>
+      </c>
+      <c r="C22" t="s">
+        <v>299</v>
+      </c>
+      <c r="D22" t="s">
+        <v>193</v>
+      </c>
+      <c r="E22" t="s">
+        <v>300</v>
+      </c>
+      <c r="F22" t="s">
+        <v>301</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="B22" t="s">
-        <v>303</v>
-      </c>
-      <c r="C22" t="s">
-        <v>304</v>
-      </c>
-      <c r="D22" t="s">
-        <v>193</v>
-      </c>
-      <c r="E22" t="s">
-        <v>305</v>
-      </c>
-      <c r="F22" t="s">
-        <v>306</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B23" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C23" t="s">
-        <v>310</v>
+        <v>220</v>
       </c>
       <c r="D23" t="s">
         <v>193</v>
       </c>
       <c r="E23" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="F23" t="s">
-        <v>218</v>
+        <v>306</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>308</v>
+      </c>
+      <c r="B24" t="s">
+        <v>309</v>
+      </c>
+      <c r="C24" t="s">
+        <v>310</v>
+      </c>
+      <c r="D24" t="s">
+        <v>311</v>
+      </c>
+      <c r="E24" t="s">
+        <v>312</v>
+      </c>
+      <c r="F24" t="s">
         <v>313</v>
       </c>
-      <c r="B24" t="s">
+      <c r="H24" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="C24" t="s">
-        <v>211</v>
-      </c>
-      <c r="D24" t="s">
-        <v>193</v>
-      </c>
-      <c r="E24" t="s">
-        <v>315</v>
-      </c>
-      <c r="F24" t="s">
-        <v>316</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>315</v>
+      </c>
+      <c r="B25" t="s">
+        <v>316</v>
+      </c>
+      <c r="C25" t="s">
+        <v>317</v>
+      </c>
+      <c r="D25" t="s">
+        <v>193</v>
+      </c>
+      <c r="E25" t="s">
         <v>318</v>
       </c>
-      <c r="B25" t="s">
+      <c r="F25" t="s">
+        <v>257</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="C25" t="s">
-        <v>320</v>
-      </c>
-      <c r="D25" t="s">
-        <v>212</v>
-      </c>
-      <c r="E25" t="s">
-        <v>321</v>
-      </c>
-      <c r="F25" t="s">
-        <v>322</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>320</v>
+      </c>
+      <c r="B26" t="s">
+        <v>321</v>
+      </c>
+      <c r="C26" t="s">
+        <v>317</v>
+      </c>
+      <c r="D26" t="s">
+        <v>322</v>
+      </c>
+      <c r="E26" t="s">
+        <v>323</v>
+      </c>
+      <c r="F26" t="s">
+        <v>200</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="B26" t="s">
-        <v>325</v>
-      </c>
-      <c r="C26" t="s">
-        <v>326</v>
-      </c>
-      <c r="D26" t="s">
-        <v>193</v>
-      </c>
-      <c r="E26" t="s">
-        <v>194</v>
-      </c>
-      <c r="F26" t="s">
-        <v>327</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>325</v>
       </c>
       <c r="B27" t="s">
+        <v>326</v>
+      </c>
+      <c r="C27" t="s">
+        <v>293</v>
+      </c>
+      <c r="D27" t="s">
+        <v>193</v>
+      </c>
+      <c r="E27" t="s">
+        <v>327</v>
+      </c>
+      <c r="F27" t="s">
+        <v>328</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="C27" t="s">
-        <v>330</v>
-      </c>
-      <c r="D27" t="s">
-        <v>193</v>
-      </c>
-      <c r="E27" t="s">
-        <v>331</v>
-      </c>
-      <c r="F27" t="s">
-        <v>332</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>113</v>
+        <v>330</v>
       </c>
       <c r="B28" t="s">
+        <v>331</v>
+      </c>
+      <c r="C28" t="s">
+        <v>332</v>
+      </c>
+      <c r="D28" t="s">
+        <v>274</v>
+      </c>
+      <c r="E28" t="s">
+        <v>333</v>
+      </c>
+      <c r="F28" t="s">
+        <v>195</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="C28" t="s">
-        <v>335</v>
-      </c>
-      <c r="D28" t="s">
-        <v>193</v>
-      </c>
-      <c r="E28" t="s">
-        <v>336</v>
-      </c>
-      <c r="F28" t="s">
-        <v>337</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>113</v>
+        <v>335</v>
       </c>
       <c r="B29" t="s">
+        <v>336</v>
+      </c>
+      <c r="C29" t="s">
+        <v>293</v>
+      </c>
+      <c r="D29" t="s">
+        <v>225</v>
+      </c>
+      <c r="E29" t="s">
+        <v>337</v>
+      </c>
+      <c r="F29" t="s">
+        <v>338</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="C29" t="s">
-        <v>340</v>
-      </c>
-      <c r="D29" t="s">
-        <v>193</v>
-      </c>
-      <c r="E29" t="s">
-        <v>341</v>
-      </c>
-      <c r="F29" t="s">
-        <v>342</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>340</v>
       </c>
       <c r="B30" t="s">
+        <v>341</v>
+      </c>
+      <c r="C30" t="s">
+        <v>220</v>
+      </c>
+      <c r="D30" t="s">
+        <v>193</v>
+      </c>
+      <c r="E30" t="s">
+        <v>342</v>
+      </c>
+      <c r="F30" t="s">
+        <v>343</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="C30" t="s">
-        <v>345</v>
-      </c>
-      <c r="D30" t="s">
-        <v>193</v>
-      </c>
-      <c r="E30" t="s">
-        <v>194</v>
-      </c>
-      <c r="F30" t="s">
-        <v>346</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>345</v>
+      </c>
+      <c r="B31" t="s">
+        <v>346</v>
+      </c>
+      <c r="C31" t="s">
+        <v>251</v>
+      </c>
+      <c r="D31" t="s">
+        <v>193</v>
+      </c>
+      <c r="E31" t="s">
+        <v>347</v>
+      </c>
+      <c r="F31" t="s">
         <v>348</v>
       </c>
-      <c r="B31" t="s">
+      <c r="H31" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="C31" t="s">
-        <v>350</v>
-      </c>
-      <c r="D31" t="s">
-        <v>212</v>
-      </c>
-      <c r="E31" t="s">
-        <v>351</v>
-      </c>
-      <c r="F31" t="s">
-        <v>352</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>350</v>
+      </c>
+      <c r="B32" t="s">
+        <v>351</v>
+      </c>
+      <c r="C32" t="s">
+        <v>210</v>
+      </c>
+      <c r="D32" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32" t="s">
+        <v>352</v>
+      </c>
+      <c r="F32" t="s">
+        <v>353</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="B32" t="s">
-        <v>355</v>
-      </c>
-      <c r="C32" t="s">
-        <v>356</v>
-      </c>
-      <c r="D32" t="s">
-        <v>193</v>
-      </c>
-      <c r="E32" t="s">
-        <v>357</v>
-      </c>
-      <c r="F32" t="s">
-        <v>358</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B33" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C33" t="s">
-        <v>362</v>
+        <v>220</v>
       </c>
       <c r="D33" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="E33" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="F33" t="s">
+        <v>357</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B34" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C34" t="s">
-        <v>367</v>
+        <v>299</v>
       </c>
       <c r="D34" t="s">
         <v>193</v>
       </c>
       <c r="E34" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F34" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B35" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="C35" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="D35" t="s">
         <v>193</v>
       </c>
       <c r="E35" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="F35" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="B36" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C36" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D36" t="s">
         <v>193</v>
       </c>
       <c r="E36" t="s">
-        <v>194</v>
+        <v>372</v>
       </c>
       <c r="F36" t="s">
-        <v>194</v>
+        <v>373</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>380</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C37" t="s">
-        <v>234</v>
+        <v>376</v>
       </c>
       <c r="D37" t="s">
         <v>193</v>
       </c>
       <c r="E37" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F37" t="s">
-        <v>322</v>
+        <v>378</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" t="s">
+        <v>380</v>
+      </c>
+      <c r="C38" t="s">
+        <v>381</v>
+      </c>
+      <c r="D38" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" t="s">
+        <v>382</v>
+      </c>
+      <c r="F38" t="s">
+        <v>383</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="B38" t="s">
-        <v>385</v>
-      </c>
-      <c r="C38" t="s">
-        <v>340</v>
-      </c>
-      <c r="D38" t="s">
-        <v>193</v>
-      </c>
-      <c r="E38" t="s">
-        <v>386</v>
-      </c>
-      <c r="F38" t="s">
-        <v>290</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>388</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C39" t="s">
-        <v>211</v>
+        <v>376</v>
       </c>
       <c r="D39" t="s">
         <v>193</v>
       </c>
       <c r="E39" t="s">
-        <v>289</v>
+        <v>377</v>
       </c>
       <c r="F39" t="s">
-        <v>194</v>
+        <v>378</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>387</v>
+      </c>
+      <c r="B40" t="s">
+        <v>388</v>
+      </c>
+      <c r="C40" t="s">
+        <v>389</v>
+      </c>
+      <c r="D40" t="s">
+        <v>193</v>
+      </c>
+      <c r="E40" t="s">
+        <v>390</v>
+      </c>
+      <c r="F40" t="s">
         <v>391</v>
       </c>
-      <c r="B40" t="s">
+      <c r="H40" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="C40" t="s">
-        <v>393</v>
-      </c>
-      <c r="D40" t="s">
-        <v>193</v>
-      </c>
-      <c r="E40" t="s">
-        <v>394</v>
-      </c>
-      <c r="F40" t="s">
-        <v>395</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B41" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C41" t="s">
-        <v>211</v>
+        <v>251</v>
       </c>
       <c r="D41" t="s">
         <v>193</v>
       </c>
       <c r="E41" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="F41" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>397</v>
+      </c>
+      <c r="B42" t="s">
+        <v>398</v>
+      </c>
+      <c r="C42" t="s">
+        <v>399</v>
+      </c>
+      <c r="D42" t="s">
+        <v>193</v>
+      </c>
+      <c r="E42" t="s">
+        <v>400</v>
+      </c>
+      <c r="F42" t="s">
+        <v>401</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="B42" t="s">
-        <v>403</v>
-      </c>
-      <c r="C42" t="s">
-        <v>404</v>
-      </c>
-      <c r="D42" t="s">
-        <v>193</v>
-      </c>
-      <c r="E42" t="s">
-        <v>405</v>
-      </c>
-      <c r="F42" t="s">
-        <v>406</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B43" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C43" t="s">
-        <v>410</v>
+        <v>220</v>
       </c>
       <c r="D43" t="s">
         <v>193</v>
       </c>
       <c r="E43" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="F43" t="s">
-        <v>412</v>
+        <v>200</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="B44" t="s">
-        <v>238</v>
+        <v>408</v>
       </c>
       <c r="C44" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D44" t="s">
         <v>193</v>
       </c>
       <c r="E44" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="F44" t="s">
-        <v>194</v>
+        <v>286</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B45" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C45" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D45" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="E45" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="F45" t="s">
-        <v>422</v>
+        <v>257</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B46" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="C46" t="s">
-        <v>426</v>
+        <v>220</v>
       </c>
       <c r="D46" t="s">
         <v>193</v>
       </c>
       <c r="E46" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="F46" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="B47" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C47" t="s">
-        <v>211</v>
+        <v>424</v>
       </c>
       <c r="D47" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="E47" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="F47" t="s">
-        <v>433</v>
+        <v>306</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="B48" t="s">
-        <v>325</v>
+        <v>428</v>
       </c>
       <c r="C48" t="s">
-        <v>326</v>
+        <v>429</v>
       </c>
       <c r="D48" t="s">
         <v>193</v>
       </c>
       <c r="E48" t="s">
-        <v>436</v>
+        <v>200</v>
       </c>
       <c r="F48" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>439</v>
+        <v>113</v>
       </c>
       <c r="B49" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C49" t="s">
-        <v>261</v>
+        <v>433</v>
       </c>
       <c r="D49" t="s">
         <v>193</v>
       </c>
       <c r="E49" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="F49" t="s">
-        <v>194</v>
+        <v>435</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>443</v>
+        <v>113</v>
       </c>
       <c r="B50" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="C50" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="D50" t="s">
         <v>193</v>
       </c>
       <c r="E50" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="F50" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>449</v>
+        <v>113</v>
       </c>
       <c r="B51" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="C51" t="s">
-        <v>451</v>
+        <v>192</v>
       </c>
       <c r="D51" t="s">
         <v>193</v>
       </c>
       <c r="E51" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="F51" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>455</v>
+        <v>113</v>
       </c>
       <c r="B52" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="C52" t="s">
-        <v>138</v>
+        <v>447</v>
       </c>
       <c r="D52" t="s">
         <v>193</v>
       </c>
       <c r="E52" t="s">
-        <v>457</v>
+        <v>200</v>
       </c>
       <c r="F52" t="s">
-        <v>458</v>
+        <v>281</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>460</v>
+        <v>113</v>
       </c>
       <c r="B53" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="C53" t="s">
-        <v>261</v>
+        <v>450</v>
       </c>
       <c r="D53" t="s">
-        <v>462</v>
+        <v>193</v>
       </c>
       <c r="E53" t="s">
-        <v>463</v>
+        <v>318</v>
       </c>
       <c r="F53" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="B54" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="C54" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="D54" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="E54" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="F54" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="B55" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="C55" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="D55" t="s">
         <v>193</v>
       </c>
       <c r="E55" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="F55" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="B56" t="s">
-        <v>473</v>
+        <v>191</v>
       </c>
       <c r="C56" t="s">
-        <v>478</v>
+        <v>192</v>
       </c>
       <c r="D56" t="s">
         <v>193</v>
       </c>
       <c r="E56" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="F56" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>469</v>
+      </c>
+      <c r="B57" t="s">
+        <v>470</v>
+      </c>
+      <c r="C57" t="s">
+        <v>471</v>
+      </c>
+      <c r="D57" t="s">
+        <v>193</v>
+      </c>
+      <c r="E57" t="s">
         <v>472</v>
       </c>
-      <c r="B57" t="s">
+      <c r="F57" t="s">
         <v>473</v>
       </c>
-      <c r="C57" t="s">
-        <v>480</v>
-      </c>
-      <c r="D57" t="s">
-        <v>193</v>
-      </c>
-      <c r="E57" t="s">
-        <v>475</v>
-      </c>
-      <c r="F57" t="s">
-        <v>476</v>
-      </c>
       <c r="H57" s="2" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B58" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="C58" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="D58" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="E58" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="F58" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="B59" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C59" t="s">
-        <v>490</v>
+        <v>317</v>
       </c>
       <c r="D59" t="s">
         <v>193</v>
       </c>
       <c r="E59" t="s">
-        <v>491</v>
+        <v>327</v>
       </c>
       <c r="F59" t="s">
-        <v>296</v>
+        <v>482</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="B60" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C60" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="D60" t="s">
         <v>193</v>
       </c>
       <c r="E60" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="F60" t="s">
-        <v>194</v>
+        <v>488</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="B61" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C61" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="D61" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
       <c r="E61" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="F61" t="s">
-        <v>274</v>
+        <v>494</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B62" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C62" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D62" t="s">
         <v>193</v>
       </c>
       <c r="E62" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="F62" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B63" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C63" t="s">
-        <v>211</v>
+        <v>317</v>
       </c>
       <c r="D63" t="s">
         <v>193</v>
       </c>
       <c r="E63" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="F63" t="s">
-        <v>194</v>
+        <v>306</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B64" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C64" t="s">
-        <v>211</v>
+        <v>507</v>
       </c>
       <c r="D64" t="s">
         <v>193</v>
       </c>
       <c r="E64" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="F64" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="B65" t="s">
+        <v>481</v>
+      </c>
+      <c r="C65" t="s">
+        <v>317</v>
+      </c>
+      <c r="D65" t="s">
+        <v>311</v>
+      </c>
+      <c r="E65" t="s">
         <v>512</v>
       </c>
-      <c r="C65" t="s">
-        <v>517</v>
-      </c>
-      <c r="D65" t="s">
-        <v>193</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>513</v>
       </c>
-      <c r="F65" t="s">
+      <c r="H65" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>515</v>
+      </c>
+      <c r="B66" t="s">
+        <v>516</v>
+      </c>
+      <c r="C66" t="s">
+        <v>517</v>
+      </c>
+      <c r="D66" t="s">
+        <v>193</v>
+      </c>
+      <c r="E66" t="s">
+        <v>518</v>
+      </c>
+      <c r="F66" t="s">
         <v>519</v>
       </c>
-      <c r="B66" t="s">
+      <c r="H66" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="C66" t="s">
-        <v>261</v>
-      </c>
-      <c r="D66" t="s">
-        <v>193</v>
-      </c>
-      <c r="E66" t="s">
-        <v>521</v>
-      </c>
-      <c r="F66" t="s">
-        <v>522</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>521</v>
+      </c>
+      <c r="B67" t="s">
+        <v>522</v>
+      </c>
+      <c r="C67" t="s">
+        <v>523</v>
+      </c>
+      <c r="D67" t="s">
+        <v>193</v>
+      </c>
+      <c r="E67" t="s">
         <v>524</v>
       </c>
-      <c r="B67" t="s">
+      <c r="F67" t="s">
         <v>525</v>
       </c>
-      <c r="C67" t="s">
+      <c r="H67" s="2" t="s">
         <v>526</v>
-      </c>
-      <c r="D67" t="s">
-        <v>212</v>
-      </c>
-      <c r="E67" t="s">
-        <v>527</v>
-      </c>
-      <c r="F67" t="s">
-        <v>528</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B68" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C68" t="s">
-        <v>532</v>
+        <v>220</v>
       </c>
       <c r="D68" t="s">
         <v>193</v>
       </c>
       <c r="E68" t="s">
-        <v>533</v>
+        <v>200</v>
       </c>
       <c r="F68" t="s">
-        <v>534</v>
+        <v>200</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="B69" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="C69" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="D69" t="s">
         <v>193</v>
       </c>
       <c r="E69" t="s">
-        <v>394</v>
+        <v>503</v>
       </c>
       <c r="F69" t="s">
-        <v>538</v>
+        <v>306</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="B70" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="C70" t="s">
-        <v>542</v>
+        <v>192</v>
       </c>
       <c r="D70" t="s">
         <v>193</v>
       </c>
       <c r="E70" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="F70" t="s">
-        <v>544</v>
+        <v>378</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="B71" t="s">
-        <v>191</v>
+        <v>538</v>
       </c>
       <c r="C71" t="s">
-        <v>547</v>
+        <v>220</v>
       </c>
       <c r="D71" t="s">
         <v>193</v>
       </c>
       <c r="E71" t="s">
-        <v>194</v>
+        <v>377</v>
       </c>
       <c r="F71" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="B72" t="s">
-        <v>191</v>
+        <v>541</v>
       </c>
       <c r="C72" t="s">
-        <v>547</v>
+        <v>498</v>
       </c>
       <c r="D72" t="s">
         <v>193</v>
       </c>
       <c r="E72" t="s">
-        <v>194</v>
+        <v>542</v>
       </c>
       <c r="F72" t="s">
-        <v>195</v>
+        <v>543</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B73" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C73" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D73" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="E73" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="F73" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="B74" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="C74" t="s">
-        <v>404</v>
+        <v>523</v>
       </c>
       <c r="D74" t="s">
         <v>193</v>
       </c>
       <c r="E74" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="F74" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="B75" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="C75" t="s">
-        <v>420</v>
+        <v>220</v>
       </c>
       <c r="D75" t="s">
         <v>193</v>
       </c>
       <c r="E75" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="F75" t="s">
-        <v>306</v>
+        <v>558</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="B76" t="s">
+        <v>561</v>
+      </c>
+      <c r="C76" t="s">
+        <v>205</v>
+      </c>
+      <c r="D76" t="s">
+        <v>193</v>
+      </c>
+      <c r="E76" t="s">
         <v>562</v>
       </c>
-      <c r="C76" t="s">
-        <v>420</v>
-      </c>
-      <c r="D76" t="s">
-        <v>193</v>
-      </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>563</v>
       </c>
-      <c r="F76" t="s">
-        <v>306</v>
-      </c>
       <c r="H76" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>565</v>
+      </c>
+      <c r="B77" t="s">
+        <v>566</v>
+      </c>
+      <c r="C77" t="s">
         <v>567</v>
       </c>
-      <c r="B77" t="s">
+      <c r="D77" t="s">
+        <v>193</v>
+      </c>
+      <c r="E77" t="s">
         <v>568</v>
       </c>
-      <c r="C77" t="s">
-        <v>211</v>
-      </c>
-      <c r="D77" t="s">
-        <v>193</v>
-      </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
+        <v>257</v>
+      </c>
+      <c r="H77" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="F77" t="s">
-        <v>570</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>570</v>
+      </c>
+      <c r="B78" t="s">
+        <v>571</v>
+      </c>
+      <c r="C78" t="s">
         <v>572</v>
       </c>
-      <c r="B78" t="s">
+      <c r="D78" t="s">
+        <v>193</v>
+      </c>
+      <c r="E78" t="s">
         <v>573</v>
       </c>
-      <c r="C78" t="s">
+      <c r="F78" t="s">
         <v>574</v>
       </c>
-      <c r="D78" t="s">
-        <v>193</v>
-      </c>
-      <c r="E78" t="s">
-        <v>194</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="H78" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B79" t="s">
-        <v>573</v>
+        <v>321</v>
       </c>
       <c r="C79" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D79" t="s">
         <v>193</v>
       </c>
       <c r="E79" t="s">
-        <v>194</v>
+        <v>578</v>
       </c>
       <c r="F79" t="s">
-        <v>575</v>
+        <v>200</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="B80" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C80" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="D80" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="E80" t="s">
-        <v>194</v>
+        <v>582</v>
       </c>
       <c r="F80" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>579</v>
+        <v>584</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>585</v>
+      </c>
+      <c r="B81" t="s">
+        <v>586</v>
+      </c>
+      <c r="C81" t="s">
+        <v>587</v>
+      </c>
+      <c r="D81" t="s">
+        <v>193</v>
+      </c>
+      <c r="E81" t="s">
+        <v>588</v>
+      </c>
+      <c r="F81" t="s">
+        <v>589</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>591</v>
+      </c>
+      <c r="B82" t="s">
+        <v>191</v>
+      </c>
+      <c r="C82" t="s">
+        <v>192</v>
+      </c>
+      <c r="D82" t="s">
+        <v>225</v>
+      </c>
+      <c r="E82" t="s">
+        <v>592</v>
+      </c>
+      <c r="F82" t="s">
+        <v>195</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>594</v>
+      </c>
+      <c r="B83" t="s">
+        <v>595</v>
+      </c>
+      <c r="C83" t="s">
+        <v>220</v>
+      </c>
+      <c r="D83" t="s">
+        <v>193</v>
+      </c>
+      <c r="E83" t="s">
+        <v>596</v>
+      </c>
+      <c r="F83" t="s">
+        <v>597</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>599</v>
+      </c>
+      <c r="B84" t="s">
+        <v>428</v>
+      </c>
+      <c r="C84" t="s">
+        <v>429</v>
+      </c>
+      <c r="D84" t="s">
+        <v>193</v>
+      </c>
+      <c r="E84" t="s">
+        <v>600</v>
+      </c>
+      <c r="F84" t="s">
+        <v>601</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>603</v>
+      </c>
+      <c r="B85" t="s">
+        <v>604</v>
+      </c>
+      <c r="C85" t="s">
+        <v>251</v>
+      </c>
+      <c r="D85" t="s">
+        <v>193</v>
+      </c>
+      <c r="E85" t="s">
+        <v>605</v>
+      </c>
+      <c r="F85" t="s">
+        <v>200</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>607</v>
+      </c>
+      <c r="B86" t="s">
+        <v>608</v>
+      </c>
+      <c r="C86" t="s">
+        <v>609</v>
+      </c>
+      <c r="D86" t="s">
+        <v>193</v>
+      </c>
+      <c r="E86" t="s">
+        <v>610</v>
+      </c>
+      <c r="F86" t="s">
+        <v>611</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>613</v>
+      </c>
+      <c r="B87" t="s">
+        <v>614</v>
+      </c>
+      <c r="C87" t="s">
+        <v>615</v>
+      </c>
+      <c r="D87" t="s">
+        <v>193</v>
+      </c>
+      <c r="E87" t="s">
+        <v>616</v>
+      </c>
+      <c r="F87" t="s">
+        <v>617</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>619</v>
+      </c>
+      <c r="B88" t="s">
+        <v>620</v>
+      </c>
+      <c r="C88" t="s">
+        <v>621</v>
+      </c>
+      <c r="D88" t="s">
+        <v>193</v>
+      </c>
+      <c r="E88" t="s">
+        <v>622</v>
+      </c>
+      <c r="F88" t="s">
+        <v>623</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>625</v>
+      </c>
+      <c r="B89" t="s">
+        <v>626</v>
+      </c>
+      <c r="C89" t="s">
+        <v>627</v>
+      </c>
+      <c r="D89" t="s">
+        <v>193</v>
+      </c>
+      <c r="E89" t="s">
+        <v>628</v>
+      </c>
+      <c r="F89" t="s">
+        <v>420</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>630</v>
+      </c>
+      <c r="B90" t="s">
+        <v>631</v>
+      </c>
+      <c r="C90" t="s">
+        <v>138</v>
+      </c>
+      <c r="D90" t="s">
+        <v>193</v>
+      </c>
+      <c r="E90" t="s">
+        <v>632</v>
+      </c>
+      <c r="F90" t="s">
+        <v>633</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>635</v>
+      </c>
+      <c r="B91" t="s">
+        <v>636</v>
+      </c>
+      <c r="C91" t="s">
+        <v>251</v>
+      </c>
+      <c r="D91" t="s">
+        <v>311</v>
+      </c>
+      <c r="E91" t="s">
+        <v>637</v>
+      </c>
+      <c r="F91" t="s">
+        <v>638</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>640</v>
+      </c>
+      <c r="B92" t="s">
+        <v>641</v>
+      </c>
+      <c r="C92" t="s">
+        <v>642</v>
+      </c>
+      <c r="D92" t="s">
+        <v>193</v>
+      </c>
+      <c r="E92" t="s">
+        <v>643</v>
+      </c>
+      <c r="F92" t="s">
+        <v>644</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>646</v>
+      </c>
+      <c r="B93" t="s">
+        <v>647</v>
+      </c>
+      <c r="C93" t="s">
+        <v>498</v>
+      </c>
+      <c r="D93" t="s">
+        <v>193</v>
+      </c>
+      <c r="E93" t="s">
+        <v>648</v>
+      </c>
+      <c r="F93" t="s">
+        <v>473</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>650</v>
+      </c>
+      <c r="B94" t="s">
+        <v>651</v>
+      </c>
+      <c r="C94" t="s">
+        <v>293</v>
+      </c>
+      <c r="D94" t="s">
+        <v>193</v>
+      </c>
+      <c r="E94" t="s">
+        <v>652</v>
+      </c>
+      <c r="F94" t="s">
+        <v>653</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>655</v>
+      </c>
+      <c r="B95" t="s">
+        <v>656</v>
+      </c>
+      <c r="C95" t="s">
+        <v>657</v>
+      </c>
+      <c r="D95" t="s">
+        <v>193</v>
+      </c>
+      <c r="E95" t="s">
+        <v>658</v>
+      </c>
+      <c r="F95" t="s">
+        <v>659</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>655</v>
+      </c>
+      <c r="B96" t="s">
+        <v>656</v>
+      </c>
+      <c r="C96" t="s">
+        <v>661</v>
+      </c>
+      <c r="D96" t="s">
+        <v>193</v>
+      </c>
+      <c r="E96" t="s">
+        <v>658</v>
+      </c>
+      <c r="F96" t="s">
+        <v>659</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>655</v>
+      </c>
+      <c r="B97" t="s">
+        <v>656</v>
+      </c>
+      <c r="C97" t="s">
+        <v>663</v>
+      </c>
+      <c r="D97" t="s">
+        <v>193</v>
+      </c>
+      <c r="E97" t="s">
+        <v>658</v>
+      </c>
+      <c r="F97" t="s">
+        <v>659</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>665</v>
+      </c>
+      <c r="B98" t="s">
+        <v>666</v>
+      </c>
+      <c r="C98" t="s">
+        <v>279</v>
+      </c>
+      <c r="D98" t="s">
+        <v>193</v>
+      </c>
+      <c r="E98" t="s">
+        <v>667</v>
+      </c>
+      <c r="F98" t="s">
+        <v>668</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>670</v>
+      </c>
+      <c r="B99" t="s">
+        <v>671</v>
+      </c>
+      <c r="C99" t="s">
+        <v>627</v>
+      </c>
+      <c r="D99" t="s">
+        <v>193</v>
+      </c>
+      <c r="E99" t="s">
+        <v>672</v>
+      </c>
+      <c r="F99" t="s">
+        <v>391</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>674</v>
+      </c>
+      <c r="B100" t="s">
+        <v>675</v>
+      </c>
+      <c r="C100" t="s">
+        <v>676</v>
+      </c>
+      <c r="D100" t="s">
+        <v>193</v>
+      </c>
+      <c r="E100" t="s">
+        <v>677</v>
+      </c>
+      <c r="F100" t="s">
+        <v>200</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>679</v>
+      </c>
+      <c r="B101" t="s">
+        <v>541</v>
+      </c>
+      <c r="C101" t="s">
+        <v>498</v>
+      </c>
+      <c r="D101" t="s">
+        <v>193</v>
+      </c>
+      <c r="E101" t="s">
+        <v>680</v>
+      </c>
+      <c r="F101" t="s">
+        <v>543</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>682</v>
+      </c>
+      <c r="B102" t="s">
+        <v>671</v>
+      </c>
+      <c r="C102" t="s">
+        <v>683</v>
+      </c>
+      <c r="D102" t="s">
+        <v>193</v>
+      </c>
+      <c r="E102" t="s">
+        <v>684</v>
+      </c>
+      <c r="F102" t="s">
+        <v>362</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>686</v>
+      </c>
+      <c r="B103" t="s">
+        <v>687</v>
+      </c>
+      <c r="C103" t="s">
+        <v>688</v>
+      </c>
+      <c r="D103" t="s">
+        <v>274</v>
+      </c>
+      <c r="E103" t="s">
+        <v>689</v>
+      </c>
+      <c r="F103" t="s">
+        <v>690</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>692</v>
+      </c>
+      <c r="B104" t="s">
+        <v>693</v>
+      </c>
+      <c r="C104" t="s">
+        <v>694</v>
+      </c>
+      <c r="D104" t="s">
+        <v>193</v>
+      </c>
+      <c r="E104" t="s">
+        <v>695</v>
+      </c>
+      <c r="F104" t="s">
+        <v>668</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>697</v>
+      </c>
+      <c r="B105" t="s">
+        <v>698</v>
+      </c>
+      <c r="C105" t="s">
+        <v>220</v>
+      </c>
+      <c r="D105" t="s">
+        <v>193</v>
+      </c>
+      <c r="E105" t="s">
+        <v>699</v>
+      </c>
+      <c r="F105" t="s">
+        <v>200</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>701</v>
+      </c>
+      <c r="B106" t="s">
+        <v>702</v>
+      </c>
+      <c r="C106" t="s">
+        <v>220</v>
+      </c>
+      <c r="D106" t="s">
+        <v>193</v>
+      </c>
+      <c r="E106" t="s">
+        <v>703</v>
+      </c>
+      <c r="F106" t="s">
+        <v>200</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>705</v>
+      </c>
+      <c r="B107" t="s">
+        <v>706</v>
+      </c>
+      <c r="C107" t="s">
+        <v>707</v>
+      </c>
+      <c r="D107" t="s">
+        <v>193</v>
+      </c>
+      <c r="E107" t="s">
+        <v>562</v>
+      </c>
+      <c r="F107" t="s">
+        <v>708</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>710</v>
+      </c>
+      <c r="B108" t="s">
+        <v>711</v>
+      </c>
+      <c r="C108" t="s">
+        <v>220</v>
+      </c>
+      <c r="D108" t="s">
+        <v>193</v>
+      </c>
+      <c r="E108" t="s">
+        <v>712</v>
+      </c>
+      <c r="F108" t="s">
+        <v>713</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>715</v>
+      </c>
+      <c r="B109" t="s">
+        <v>711</v>
+      </c>
+      <c r="C109" t="s">
+        <v>716</v>
+      </c>
+      <c r="D109" t="s">
+        <v>193</v>
+      </c>
+      <c r="E109" t="s">
+        <v>712</v>
+      </c>
+      <c r="F109" t="s">
+        <v>713</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>718</v>
+      </c>
+      <c r="B110" t="s">
+        <v>719</v>
+      </c>
+      <c r="C110" t="s">
+        <v>220</v>
+      </c>
+      <c r="D110" t="s">
+        <v>193</v>
+      </c>
+      <c r="E110" t="s">
+        <v>720</v>
+      </c>
+      <c r="F110" t="s">
+        <v>721</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>723</v>
+      </c>
+      <c r="B111" t="s">
+        <v>266</v>
+      </c>
+      <c r="C111" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" t="s">
+        <v>193</v>
+      </c>
+      <c r="E111" t="s">
+        <v>724</v>
+      </c>
+      <c r="F111" t="s">
+        <v>725</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>727</v>
+      </c>
+      <c r="B112" t="s">
+        <v>728</v>
+      </c>
+      <c r="C112" t="s">
+        <v>251</v>
+      </c>
+      <c r="D112" t="s">
+        <v>193</v>
+      </c>
+      <c r="E112" t="s">
+        <v>729</v>
+      </c>
+      <c r="F112" t="s">
+        <v>242</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>731</v>
+      </c>
+      <c r="B113" t="s">
+        <v>732</v>
+      </c>
+      <c r="C113" t="s">
+        <v>733</v>
+      </c>
+      <c r="D113" t="s">
+        <v>225</v>
+      </c>
+      <c r="E113" t="s">
+        <v>734</v>
+      </c>
+      <c r="F113" t="s">
+        <v>735</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>737</v>
+      </c>
+      <c r="B114" t="s">
+        <v>738</v>
+      </c>
+      <c r="C114" t="s">
+        <v>739</v>
+      </c>
+      <c r="D114" t="s">
+        <v>193</v>
+      </c>
+      <c r="E114" t="s">
+        <v>740</v>
+      </c>
+      <c r="F114" t="s">
+        <v>690</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>742</v>
+      </c>
+      <c r="B115" t="s">
+        <v>743</v>
+      </c>
+      <c r="C115" t="s">
+        <v>744</v>
+      </c>
+      <c r="D115" t="s">
+        <v>193</v>
+      </c>
+      <c r="E115" t="s">
+        <v>568</v>
+      </c>
+      <c r="F115" t="s">
+        <v>745</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>747</v>
+      </c>
+      <c r="B116" t="s">
+        <v>748</v>
+      </c>
+      <c r="C116" t="s">
+        <v>192</v>
+      </c>
+      <c r="D116" t="s">
+        <v>193</v>
+      </c>
+      <c r="E116" t="s">
+        <v>548</v>
+      </c>
+      <c r="F116" t="s">
+        <v>749</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>751</v>
+      </c>
+      <c r="B117" t="s">
+        <v>752</v>
+      </c>
+      <c r="C117" t="s">
+        <v>753</v>
+      </c>
+      <c r="D117" t="s">
+        <v>193</v>
+      </c>
+      <c r="E117" t="s">
+        <v>754</v>
+      </c>
+      <c r="F117" t="s">
+        <v>269</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>756</v>
+      </c>
+      <c r="B118" t="s">
+        <v>752</v>
+      </c>
+      <c r="C118" t="s">
+        <v>757</v>
+      </c>
+      <c r="D118" t="s">
+        <v>193</v>
+      </c>
+      <c r="E118" t="s">
+        <v>754</v>
+      </c>
+      <c r="F118" t="s">
+        <v>269</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>759</v>
+      </c>
+      <c r="B119" t="s">
+        <v>760</v>
+      </c>
+      <c r="C119" t="s">
+        <v>138</v>
+      </c>
+      <c r="D119" t="s">
+        <v>193</v>
+      </c>
+      <c r="E119" t="s">
+        <v>761</v>
+      </c>
+      <c r="F119" t="s">
+        <v>668</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>763</v>
+      </c>
+      <c r="B120" t="s">
+        <v>198</v>
+      </c>
+      <c r="C120" t="s">
+        <v>764</v>
+      </c>
+      <c r="D120" t="s">
+        <v>193</v>
+      </c>
+      <c r="E120" t="s">
+        <v>200</v>
+      </c>
+      <c r="F120" t="s">
+        <v>201</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>766</v>
+      </c>
+      <c r="B121" t="s">
+        <v>198</v>
+      </c>
+      <c r="C121" t="s">
+        <v>764</v>
+      </c>
+      <c r="D121" t="s">
+        <v>193</v>
+      </c>
+      <c r="E121" t="s">
+        <v>200</v>
+      </c>
+      <c r="F121" t="s">
+        <v>201</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>768</v>
+      </c>
+      <c r="B122" t="s">
+        <v>769</v>
+      </c>
+      <c r="C122" t="s">
+        <v>770</v>
+      </c>
+      <c r="D122" t="s">
+        <v>274</v>
+      </c>
+      <c r="E122" t="s">
+        <v>771</v>
+      </c>
+      <c r="F122" t="s">
+        <v>772</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>774</v>
+      </c>
+      <c r="B123" t="s">
+        <v>775</v>
+      </c>
+      <c r="C123" t="s">
+        <v>776</v>
+      </c>
+      <c r="D123" t="s">
+        <v>274</v>
+      </c>
+      <c r="E123" t="s">
+        <v>777</v>
+      </c>
+      <c r="F123" t="s">
+        <v>778</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>780</v>
+      </c>
+      <c r="B124" t="s">
+        <v>781</v>
+      </c>
+      <c r="C124" t="s">
+        <v>205</v>
+      </c>
+      <c r="D124" t="s">
+        <v>193</v>
+      </c>
+      <c r="E124" t="s">
+        <v>200</v>
+      </c>
+      <c r="F124" t="s">
+        <v>782</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>784</v>
+      </c>
+      <c r="B125" t="s">
+        <v>785</v>
+      </c>
+      <c r="C125" t="s">
+        <v>567</v>
+      </c>
+      <c r="D125" t="s">
+        <v>193</v>
+      </c>
+      <c r="E125" t="s">
+        <v>786</v>
+      </c>
+      <c r="F125" t="s">
+        <v>286</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>788</v>
+      </c>
+      <c r="B126" t="s">
+        <v>785</v>
+      </c>
+      <c r="C126" t="s">
+        <v>567</v>
+      </c>
+      <c r="D126" t="s">
+        <v>193</v>
+      </c>
+      <c r="E126" t="s">
+        <v>786</v>
+      </c>
+      <c r="F126" t="s">
+        <v>286</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>790</v>
+      </c>
+      <c r="B127" t="s">
+        <v>791</v>
+      </c>
+      <c r="C127" t="s">
+        <v>220</v>
+      </c>
+      <c r="D127" t="s">
+        <v>193</v>
+      </c>
+      <c r="E127" t="s">
+        <v>792</v>
+      </c>
+      <c r="F127" t="s">
+        <v>793</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>795</v>
+      </c>
+      <c r="B128" t="s">
+        <v>796</v>
+      </c>
+      <c r="C128" t="s">
+        <v>17</v>
+      </c>
+      <c r="D128" t="s">
+        <v>193</v>
+      </c>
+      <c r="E128" t="s">
+        <v>797</v>
+      </c>
+      <c r="F128" t="s">
+        <v>798</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>800</v>
+      </c>
+      <c r="B129" t="s">
+        <v>801</v>
+      </c>
+      <c r="C129" t="s">
+        <v>802</v>
+      </c>
+      <c r="D129" t="s">
+        <v>193</v>
+      </c>
+      <c r="E129" t="s">
+        <v>200</v>
+      </c>
+      <c r="F129" t="s">
+        <v>803</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>800</v>
+      </c>
+      <c r="B130" t="s">
+        <v>801</v>
+      </c>
+      <c r="C130" t="s">
+        <v>802</v>
+      </c>
+      <c r="D130" t="s">
+        <v>193</v>
+      </c>
+      <c r="E130" t="s">
+        <v>200</v>
+      </c>
+      <c r="F130" t="s">
+        <v>803</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>800</v>
+      </c>
+      <c r="B131" t="s">
+        <v>801</v>
+      </c>
+      <c r="C131" t="s">
+        <v>802</v>
+      </c>
+      <c r="D131" t="s">
+        <v>225</v>
+      </c>
+      <c r="E131" t="s">
+        <v>200</v>
+      </c>
+      <c r="F131" t="s">
+        <v>806</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>807</v>
       </c>
     </row>
   </sheetData>
@@ -4967,6 +6824,57 @@
     <hyperlink ref="H78" r:id="rId77"/>
     <hyperlink ref="H79" r:id="rId78"/>
     <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
